--- a/clients/1_Hamster/prognose_1_Hamster.xlsx
+++ b/clients/1_Hamster/prognose_1_Hamster.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ca0cd6497a80e2a/Documents/GitHub/LaborProject2026/clients/1_Hamster/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0CA0CD6497A80E2A/Documents/GitHub/LaborProject2026/clients/1_Hamster/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_363B342E72A8B03B8C1359B2E56801CDA2064BC5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_363B342E72A8B03B8C1359B2E56801CDA2064BC5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45A510BA-090B-4A7E-B62E-412CC38037F7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Integratie Prognose Model" sheetId="1" r:id="rId1"/>
@@ -3568,22 +3568,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3593,58 +3631,20 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3675,9 +3675,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3641406</xdr:colOff>
+      <xdr:colOff>3637596</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>15774</xdr:rowOff>
+      <xdr:rowOff>19584</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3722,9 +3722,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>7219146</xdr:colOff>
+      <xdr:colOff>7222956</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>15667</xdr:rowOff>
+      <xdr:rowOff>19477</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3769,9 +3769,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3641118</xdr:colOff>
+      <xdr:colOff>3637308</xdr:colOff>
       <xdr:row>87</xdr:row>
-      <xdr:rowOff>2151263</xdr:rowOff>
+      <xdr:rowOff>2155073</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3816,9 +3816,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3642076</xdr:colOff>
+      <xdr:colOff>3638266</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>1884514</xdr:rowOff>
+      <xdr:rowOff>1888324</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3865,7 +3865,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>3656168</xdr:colOff>
       <xdr:row>70</xdr:row>
-      <xdr:rowOff>2536365</xdr:rowOff>
+      <xdr:rowOff>2532555</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3904,7 +3904,7 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3685190</xdr:colOff>
+      <xdr:colOff>3683285</xdr:colOff>
       <xdr:row>70</xdr:row>
       <xdr:rowOff>39414</xdr:rowOff>
     </xdr:from>
@@ -3935,8 +3935,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6043449" y="8973207"/>
-          <a:ext cx="3600000" cy="2520000"/>
+          <a:off x="6955403" y="19694532"/>
+          <a:ext cx="3609525" cy="2533335"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3957,9 +3957,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3637604</xdr:colOff>
+      <xdr:colOff>3641414</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>2569033</xdr:rowOff>
+      <xdr:rowOff>2572843</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4004,9 +4004,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>7223310</xdr:colOff>
+      <xdr:colOff>7219500</xdr:colOff>
       <xdr:row>116</xdr:row>
-      <xdr:rowOff>2532755</xdr:rowOff>
+      <xdr:rowOff>2536565</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4051,9 +4051,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3636278</xdr:colOff>
+      <xdr:colOff>3640088</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>2569033</xdr:rowOff>
+      <xdr:rowOff>2572843</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4098,9 +4098,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3673879</xdr:colOff>
+      <xdr:colOff>3677689</xdr:colOff>
       <xdr:row>141</xdr:row>
-      <xdr:rowOff>11472</xdr:rowOff>
+      <xdr:rowOff>15282</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4145,9 +4145,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3673880</xdr:colOff>
+      <xdr:colOff>3677690</xdr:colOff>
       <xdr:row>144</xdr:row>
-      <xdr:rowOff>11471</xdr:rowOff>
+      <xdr:rowOff>15281</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4192,9 +4192,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1426710</xdr:colOff>
+      <xdr:colOff>1430520</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>18915</xdr:rowOff>
+      <xdr:rowOff>22725</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4241,7 +4241,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>1527675</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>2000115</xdr:rowOff>
+      <xdr:rowOff>2003925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4286,9 +4286,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1352415</xdr:colOff>
+      <xdr:colOff>1356225</xdr:colOff>
       <xdr:row>66</xdr:row>
-      <xdr:rowOff>57015</xdr:rowOff>
+      <xdr:rowOff>60825</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4427,9 +4427,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1390515</xdr:colOff>
+      <xdr:colOff>1394325</xdr:colOff>
       <xdr:row>106</xdr:row>
-      <xdr:rowOff>18915</xdr:rowOff>
+      <xdr:rowOff>22725</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4521,7 +4521,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1390515</xdr:colOff>
+      <xdr:colOff>1394325</xdr:colOff>
       <xdr:row>152</xdr:row>
       <xdr:rowOff>117975</xdr:rowOff>
     </xdr:to>
@@ -4568,9 +4568,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>5276850</xdr:colOff>
+      <xdr:colOff>5273040</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>168224</xdr:rowOff>
+      <xdr:rowOff>172034</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4615,9 +4615,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>5240655</xdr:colOff>
+      <xdr:colOff>5236845</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>15826</xdr:rowOff>
+      <xdr:rowOff>19636</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4664,7 +4664,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>5295900</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>2573655</xdr:rowOff>
+      <xdr:rowOff>2569845</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4709,9 +4709,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>5276850</xdr:colOff>
+      <xdr:colOff>5273040</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>2113470</xdr:rowOff>
+      <xdr:rowOff>2117280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4758,7 +4758,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>4381500</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>133349</xdr:rowOff>
+      <xdr:rowOff>137159</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4803,9 +4803,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>9052559</xdr:colOff>
+      <xdr:colOff>9048749</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4852,7 +4852,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>7696200</xdr:colOff>
       <xdr:row>90</xdr:row>
-      <xdr:rowOff>1885423</xdr:rowOff>
+      <xdr:rowOff>1889233</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4897,7 +4897,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>4210050</xdr:colOff>
+      <xdr:colOff>4206240</xdr:colOff>
       <xdr:row>100</xdr:row>
       <xdr:rowOff>2705100</xdr:rowOff>
     </xdr:to>
@@ -4944,9 +4944,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>9660255</xdr:colOff>
+      <xdr:colOff>9656445</xdr:colOff>
       <xdr:row>100</xdr:row>
-      <xdr:rowOff>2724150</xdr:rowOff>
+      <xdr:rowOff>2720340</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5038,7 +5038,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>7216140</xdr:colOff>
+      <xdr:colOff>7219950</xdr:colOff>
       <xdr:row>106</xdr:row>
       <xdr:rowOff>3771485</xdr:rowOff>
     </xdr:to>
@@ -5087,7 +5087,7 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>7238999</xdr:colOff>
       <xdr:row>109</xdr:row>
-      <xdr:rowOff>3829050</xdr:rowOff>
+      <xdr:rowOff>3825240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5132,9 +5132,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>4819650</xdr:colOff>
+      <xdr:colOff>4815840</xdr:colOff>
       <xdr:row>120</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5179,7 +5179,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>8134349</xdr:colOff>
+      <xdr:colOff>8138159</xdr:colOff>
       <xdr:row>119</xdr:row>
       <xdr:rowOff>3086100</xdr:rowOff>
     </xdr:to>
@@ -5226,9 +5226,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>4435547</xdr:colOff>
+      <xdr:colOff>4439357</xdr:colOff>
       <xdr:row>172</xdr:row>
-      <xdr:rowOff>4403160</xdr:rowOff>
+      <xdr:rowOff>4399350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5273,9 +5273,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>10878577</xdr:colOff>
+      <xdr:colOff>10874767</xdr:colOff>
       <xdr:row>122</xdr:row>
-      <xdr:rowOff>4173855</xdr:rowOff>
+      <xdr:rowOff>4170045</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5320,7 +5320,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>7140240</xdr:colOff>
+      <xdr:colOff>7144050</xdr:colOff>
       <xdr:row>122</xdr:row>
       <xdr:rowOff>4150995</xdr:rowOff>
     </xdr:to>
@@ -5367,9 +5367,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>3371637</xdr:colOff>
+      <xdr:colOff>3375447</xdr:colOff>
       <xdr:row>122</xdr:row>
-      <xdr:rowOff>4130040</xdr:rowOff>
+      <xdr:rowOff>4133850</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5414,9 +5414,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1428750</xdr:colOff>
+      <xdr:colOff>1424940</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>135453</xdr:rowOff>
+      <xdr:rowOff>131643</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5767,30 +5767,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="192"/>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="194"/>
+      <c r="A1" s="166"/>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
+      <c r="G1" s="167"/>
+      <c r="H1" s="167"/>
+      <c r="I1" s="167"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="167"/>
+      <c r="L1" s="167"/>
+      <c r="M1" s="167"/>
+      <c r="N1" s="167"/>
+      <c r="O1" s="167"/>
+      <c r="P1" s="167"/>
+      <c r="Q1" s="167"/>
+      <c r="R1" s="173"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="196" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="185" t="s">
+      <c r="B2" s="184" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="96" t="s">
@@ -5814,23 +5814,23 @@
       <c r="M2" s="16"/>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
-      <c r="P2" s="183"/>
+      <c r="P2" s="195"/>
       <c r="Q2" s="151"/>
-      <c r="R2" s="187"/>
+      <c r="R2" s="174"/>
     </row>
     <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="171"/>
-      <c r="B3" s="171"/>
+      <c r="A3" s="175"/>
+      <c r="B3" s="175"/>
       <c r="C3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="170">
+      <c r="D3" s="176">
         <v>0.33329999999999999</v>
       </c>
-      <c r="E3" s="172">
+      <c r="E3" s="170">
         <v>1</v>
       </c>
-      <c r="F3" s="170">
+      <c r="F3" s="176">
         <v>0.66659999999999997</v>
       </c>
       <c r="G3" s="17"/>
@@ -5842,19 +5842,19 @@
       <c r="M3" s="19"/>
       <c r="N3" s="19"/>
       <c r="O3" s="19"/>
-      <c r="P3" s="171"/>
-      <c r="Q3" s="170"/>
-      <c r="R3" s="187"/>
+      <c r="P3" s="175"/>
+      <c r="Q3" s="176"/>
+      <c r="R3" s="174"/>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="171"/>
-      <c r="B4" s="171"/>
+      <c r="A4" s="175"/>
+      <c r="B4" s="175"/>
       <c r="C4" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="171"/>
+      <c r="D4" s="175"/>
       <c r="E4" s="181"/>
-      <c r="F4" s="171"/>
+      <c r="F4" s="175"/>
       <c r="G4" s="17"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19"/>
@@ -5864,17 +5864,17 @@
       <c r="M4" s="19"/>
       <c r="N4" s="19"/>
       <c r="O4" s="19"/>
-      <c r="P4" s="171"/>
-      <c r="Q4" s="171"/>
-      <c r="R4" s="187"/>
+      <c r="P4" s="175"/>
+      <c r="Q4" s="175"/>
+      <c r="R4" s="174"/>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="171"/>
-      <c r="B5" s="171"/>
-      <c r="C5" s="174"/>
-      <c r="D5" s="171"/>
+      <c r="A5" s="175"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="190"/>
+      <c r="D5" s="175"/>
       <c r="E5" s="181"/>
-      <c r="F5" s="171"/>
+      <c r="F5" s="175"/>
       <c r="G5" s="17"/>
       <c r="H5" s="18"/>
       <c r="I5" s="19"/>
@@ -5884,17 +5884,17 @@
       <c r="M5" s="19"/>
       <c r="N5" s="19"/>
       <c r="O5" s="19"/>
-      <c r="P5" s="171"/>
-      <c r="Q5" s="171"/>
-      <c r="R5" s="187"/>
+      <c r="P5" s="175"/>
+      <c r="Q5" s="175"/>
+      <c r="R5" s="174"/>
     </row>
     <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="171"/>
-      <c r="B6" s="171"/>
-      <c r="C6" s="175"/>
-      <c r="D6" s="171"/>
+      <c r="A6" s="175"/>
+      <c r="B6" s="175"/>
+      <c r="C6" s="191"/>
+      <c r="D6" s="175"/>
       <c r="E6" s="181"/>
-      <c r="F6" s="171"/>
+      <c r="F6" s="175"/>
       <c r="G6" s="17"/>
       <c r="H6" s="18"/>
       <c r="I6" s="19"/>
@@ -5904,17 +5904,17 @@
       <c r="M6" s="19"/>
       <c r="N6" s="19"/>
       <c r="O6" s="19"/>
-      <c r="P6" s="171"/>
-      <c r="Q6" s="171"/>
-      <c r="R6" s="187"/>
+      <c r="P6" s="175"/>
+      <c r="Q6" s="175"/>
+      <c r="R6" s="174"/>
     </row>
     <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="171"/>
-      <c r="B7" s="171"/>
-      <c r="C7" s="175"/>
-      <c r="D7" s="171"/>
+      <c r="A7" s="175"/>
+      <c r="B7" s="175"/>
+      <c r="C7" s="191"/>
+      <c r="D7" s="175"/>
       <c r="E7" s="181"/>
-      <c r="F7" s="171"/>
+      <c r="F7" s="175"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18"/>
       <c r="I7" s="19"/>
@@ -5924,17 +5924,17 @@
       <c r="M7" s="19"/>
       <c r="N7" s="19"/>
       <c r="O7" s="19"/>
-      <c r="P7" s="171"/>
-      <c r="Q7" s="171"/>
-      <c r="R7" s="187"/>
+      <c r="P7" s="175"/>
+      <c r="Q7" s="175"/>
+      <c r="R7" s="174"/>
     </row>
     <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="171"/>
-      <c r="B8" s="171"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="171"/>
+      <c r="A8" s="175"/>
+      <c r="B8" s="175"/>
+      <c r="C8" s="191"/>
+      <c r="D8" s="175"/>
       <c r="E8" s="181"/>
-      <c r="F8" s="171"/>
+      <c r="F8" s="175"/>
       <c r="G8" s="17"/>
       <c r="H8" s="18"/>
       <c r="I8" s="19"/>
@@ -5944,17 +5944,17 @@
       <c r="M8" s="19"/>
       <c r="N8" s="19"/>
       <c r="O8" s="19"/>
-      <c r="P8" s="171"/>
-      <c r="Q8" s="171"/>
-      <c r="R8" s="187"/>
+      <c r="P8" s="175"/>
+      <c r="Q8" s="175"/>
+      <c r="R8" s="174"/>
     </row>
     <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="171"/>
-      <c r="B9" s="171"/>
-      <c r="C9" s="175"/>
-      <c r="D9" s="171"/>
+      <c r="A9" s="175"/>
+      <c r="B9" s="175"/>
+      <c r="C9" s="191"/>
+      <c r="D9" s="175"/>
       <c r="E9" s="181"/>
-      <c r="F9" s="171"/>
+      <c r="F9" s="175"/>
       <c r="G9" s="17"/>
       <c r="H9" s="18"/>
       <c r="I9" s="19"/>
@@ -5964,17 +5964,17 @@
       <c r="M9" s="19"/>
       <c r="N9" s="19"/>
       <c r="O9" s="19"/>
-      <c r="P9" s="171"/>
-      <c r="Q9" s="171"/>
-      <c r="R9" s="187"/>
+      <c r="P9" s="175"/>
+      <c r="Q9" s="175"/>
+      <c r="R9" s="174"/>
     </row>
     <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="171"/>
-      <c r="B10" s="171"/>
-      <c r="C10" s="175"/>
-      <c r="D10" s="171"/>
+      <c r="A10" s="175"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="191"/>
+      <c r="D10" s="175"/>
       <c r="E10" s="181"/>
-      <c r="F10" s="171"/>
+      <c r="F10" s="175"/>
       <c r="G10" s="17"/>
       <c r="H10" s="18"/>
       <c r="I10" s="19"/>
@@ -5984,17 +5984,17 @@
       <c r="M10" s="19"/>
       <c r="N10" s="19"/>
       <c r="O10" s="19"/>
-      <c r="P10" s="171"/>
-      <c r="Q10" s="171"/>
-      <c r="R10" s="187"/>
+      <c r="P10" s="175"/>
+      <c r="Q10" s="175"/>
+      <c r="R10" s="174"/>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="171"/>
-      <c r="B11" s="171"/>
-      <c r="C11" s="175"/>
-      <c r="D11" s="171"/>
+      <c r="A11" s="175"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="191"/>
+      <c r="D11" s="175"/>
       <c r="E11" s="181"/>
-      <c r="F11" s="171"/>
+      <c r="F11" s="175"/>
       <c r="G11" s="17"/>
       <c r="H11" s="18"/>
       <c r="I11" s="19"/>
@@ -6004,17 +6004,17 @@
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
       <c r="O11" s="19"/>
-      <c r="P11" s="171"/>
-      <c r="Q11" s="171"/>
-      <c r="R11" s="187"/>
+      <c r="P11" s="175"/>
+      <c r="Q11" s="175"/>
+      <c r="R11" s="174"/>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="171"/>
-      <c r="B12" s="171"/>
-      <c r="C12" s="175"/>
-      <c r="D12" s="171"/>
+      <c r="A12" s="175"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="191"/>
+      <c r="D12" s="175"/>
       <c r="E12" s="181"/>
-      <c r="F12" s="171"/>
+      <c r="F12" s="175"/>
       <c r="G12" s="17"/>
       <c r="H12" s="18"/>
       <c r="I12" s="19"/>
@@ -6024,17 +6024,17 @@
       <c r="M12" s="19"/>
       <c r="N12" s="19"/>
       <c r="O12" s="19"/>
-      <c r="P12" s="171"/>
-      <c r="Q12" s="171"/>
-      <c r="R12" s="187"/>
+      <c r="P12" s="175"/>
+      <c r="Q12" s="175"/>
+      <c r="R12" s="174"/>
     </row>
     <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="171"/>
-      <c r="B13" s="171"/>
-      <c r="C13" s="175"/>
-      <c r="D13" s="171"/>
+      <c r="A13" s="175"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="191"/>
+      <c r="D13" s="175"/>
       <c r="E13" s="181"/>
-      <c r="F13" s="171"/>
+      <c r="F13" s="175"/>
       <c r="G13" s="17"/>
       <c r="H13" s="18"/>
       <c r="I13" s="19"/>
@@ -6044,17 +6044,17 @@
       <c r="M13" s="19"/>
       <c r="N13" s="19"/>
       <c r="O13" s="19"/>
-      <c r="P13" s="171"/>
-      <c r="Q13" s="171"/>
-      <c r="R13" s="187"/>
+      <c r="P13" s="175"/>
+      <c r="Q13" s="175"/>
+      <c r="R13" s="174"/>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="171"/>
-      <c r="B14" s="171"/>
-      <c r="C14" s="175"/>
-      <c r="D14" s="171"/>
+      <c r="A14" s="175"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="191"/>
+      <c r="D14" s="175"/>
       <c r="E14" s="181"/>
-      <c r="F14" s="171"/>
+      <c r="F14" s="175"/>
       <c r="G14" s="17"/>
       <c r="H14" s="18"/>
       <c r="I14" s="19"/>
@@ -6064,17 +6064,17 @@
       <c r="M14" s="19"/>
       <c r="N14" s="19"/>
       <c r="O14" s="19"/>
-      <c r="P14" s="171"/>
-      <c r="Q14" s="171"/>
-      <c r="R14" s="187"/>
+      <c r="P14" s="175"/>
+      <c r="Q14" s="175"/>
+      <c r="R14" s="174"/>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="171"/>
-      <c r="B15" s="171"/>
-      <c r="C15" s="175"/>
-      <c r="D15" s="171"/>
+      <c r="A15" s="175"/>
+      <c r="B15" s="175"/>
+      <c r="C15" s="191"/>
+      <c r="D15" s="175"/>
       <c r="E15" s="181"/>
-      <c r="F15" s="171"/>
+      <c r="F15" s="175"/>
       <c r="G15" s="17"/>
       <c r="H15" s="18"/>
       <c r="I15" s="19"/>
@@ -6084,17 +6084,17 @@
       <c r="M15" s="19"/>
       <c r="N15" s="19"/>
       <c r="O15" s="19"/>
-      <c r="P15" s="171"/>
-      <c r="Q15" s="171"/>
-      <c r="R15" s="187"/>
+      <c r="P15" s="175"/>
+      <c r="Q15" s="175"/>
+      <c r="R15" s="174"/>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="171"/>
-      <c r="B16" s="171"/>
-      <c r="C16" s="175"/>
-      <c r="D16" s="171"/>
+      <c r="A16" s="175"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="191"/>
+      <c r="D16" s="175"/>
       <c r="E16" s="181"/>
-      <c r="F16" s="171"/>
+      <c r="F16" s="175"/>
       <c r="G16" s="17"/>
       <c r="H16" s="18"/>
       <c r="I16" s="19"/>
@@ -6104,17 +6104,17 @@
       <c r="M16" s="19"/>
       <c r="N16" s="19"/>
       <c r="O16" s="19"/>
-      <c r="P16" s="171"/>
-      <c r="Q16" s="171"/>
-      <c r="R16" s="187"/>
+      <c r="P16" s="175"/>
+      <c r="Q16" s="175"/>
+      <c r="R16" s="174"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="171"/>
-      <c r="B17" s="171"/>
-      <c r="C17" s="175"/>
-      <c r="D17" s="171"/>
+      <c r="A17" s="175"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="191"/>
+      <c r="D17" s="175"/>
       <c r="E17" s="181"/>
-      <c r="F17" s="171"/>
+      <c r="F17" s="175"/>
       <c r="G17" s="17"/>
       <c r="H17" s="18"/>
       <c r="I17" s="19"/>
@@ -6124,16 +6124,16 @@
       <c r="M17" s="19"/>
       <c r="N17" s="19"/>
       <c r="O17" s="19"/>
-      <c r="P17" s="171"/>
-      <c r="Q17" s="171"/>
-      <c r="R17" s="187"/>
+      <c r="P17" s="175"/>
+      <c r="Q17" s="175"/>
+      <c r="R17" s="174"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="171"/>
-      <c r="B18" s="171"/>
-      <c r="C18" s="175"/>
+      <c r="A18" s="175"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="191"/>
       <c r="D18" s="169"/>
-      <c r="E18" s="167"/>
+      <c r="E18" s="171"/>
       <c r="F18" s="169"/>
       <c r="G18" s="17"/>
       <c r="H18" s="18"/>
@@ -6144,13 +6144,13 @@
       <c r="M18" s="19"/>
       <c r="N18" s="19"/>
       <c r="O18" s="19"/>
-      <c r="P18" s="171"/>
+      <c r="P18" s="175"/>
       <c r="Q18" s="169"/>
-      <c r="R18" s="187"/>
+      <c r="R18" s="174"/>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="171"/>
-      <c r="B19" s="171"/>
+      <c r="A19" s="175"/>
+      <c r="B19" s="175"/>
       <c r="C19" s="96" t="s">
         <v>8</v>
       </c>
@@ -6172,20 +6172,20 @@
       <c r="M19" s="20"/>
       <c r="N19" s="20"/>
       <c r="O19" s="20"/>
-      <c r="P19" s="171"/>
+      <c r="P19" s="175"/>
       <c r="Q19" s="152"/>
-      <c r="R19" s="187"/>
+      <c r="R19" s="174"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="171"/>
-      <c r="B20" s="171"/>
+      <c r="A20" s="175"/>
+      <c r="B20" s="175"/>
       <c r="C20" s="30" t="s">
         <v>6</v>
       </c>
       <c r="D20" s="168">
         <v>1</v>
       </c>
-      <c r="E20" s="166">
+      <c r="E20" s="172">
         <v>0.33329999999999999</v>
       </c>
       <c r="F20" s="168">
@@ -6200,21 +6200,21 @@
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="18"/>
-      <c r="P20" s="171"/>
-      <c r="Q20" s="170">
+      <c r="P20" s="175"/>
+      <c r="Q20" s="176">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R20" s="187"/>
+      <c r="R20" s="174"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="171"/>
-      <c r="B21" s="171"/>
+      <c r="A21" s="175"/>
+      <c r="B21" s="175"/>
       <c r="C21" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="171"/>
+      <c r="D21" s="175"/>
       <c r="E21" s="181"/>
-      <c r="F21" s="171"/>
+      <c r="F21" s="175"/>
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
       <c r="I21" s="18"/>
@@ -6224,17 +6224,17 @@
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="18"/>
-      <c r="P21" s="171"/>
-      <c r="Q21" s="171"/>
-      <c r="R21" s="187"/>
+      <c r="P21" s="175"/>
+      <c r="Q21" s="175"/>
+      <c r="R21" s="174"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="171"/>
-      <c r="B22" s="171"/>
-      <c r="C22" s="178"/>
-      <c r="D22" s="171"/>
+      <c r="A22" s="175"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="175"/>
       <c r="E22" s="181"/>
-      <c r="F22" s="171"/>
+      <c r="F22" s="175"/>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="18"/>
@@ -6244,17 +6244,17 @@
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
       <c r="O22" s="18"/>
-      <c r="P22" s="171"/>
-      <c r="Q22" s="171"/>
-      <c r="R22" s="187"/>
+      <c r="P22" s="175"/>
+      <c r="Q22" s="175"/>
+      <c r="R22" s="174"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="171"/>
-      <c r="B23" s="171"/>
-      <c r="C23" s="175"/>
-      <c r="D23" s="171"/>
+      <c r="A23" s="175"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="191"/>
+      <c r="D23" s="175"/>
       <c r="E23" s="181"/>
-      <c r="F23" s="171"/>
+      <c r="F23" s="175"/>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="I23" s="18"/>
@@ -6264,17 +6264,17 @@
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
       <c r="O23" s="18"/>
-      <c r="P23" s="171"/>
-      <c r="Q23" s="171"/>
-      <c r="R23" s="187"/>
+      <c r="P23" s="175"/>
+      <c r="Q23" s="175"/>
+      <c r="R23" s="174"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="171"/>
-      <c r="B24" s="171"/>
-      <c r="C24" s="175"/>
-      <c r="D24" s="171"/>
+      <c r="A24" s="175"/>
+      <c r="B24" s="175"/>
+      <c r="C24" s="191"/>
+      <c r="D24" s="175"/>
       <c r="E24" s="181"/>
-      <c r="F24" s="171"/>
+      <c r="F24" s="175"/>
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
       <c r="I24" s="18"/>
@@ -6284,17 +6284,17 @@
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
       <c r="O24" s="18"/>
-      <c r="P24" s="171"/>
-      <c r="Q24" s="171"/>
-      <c r="R24" s="187"/>
+      <c r="P24" s="175"/>
+      <c r="Q24" s="175"/>
+      <c r="R24" s="174"/>
     </row>
     <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="171"/>
-      <c r="B25" s="171"/>
-      <c r="C25" s="175"/>
-      <c r="D25" s="171"/>
+      <c r="A25" s="175"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="191"/>
+      <c r="D25" s="175"/>
       <c r="E25" s="181"/>
-      <c r="F25" s="171"/>
+      <c r="F25" s="175"/>
       <c r="G25" s="17"/>
       <c r="H25" s="17"/>
       <c r="I25" s="18"/>
@@ -6304,17 +6304,17 @@
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
       <c r="O25" s="18"/>
-      <c r="P25" s="171"/>
-      <c r="Q25" s="171"/>
-      <c r="R25" s="187"/>
+      <c r="P25" s="175"/>
+      <c r="Q25" s="175"/>
+      <c r="R25" s="174"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="171"/>
-      <c r="B26" s="171"/>
-      <c r="C26" s="175"/>
-      <c r="D26" s="171"/>
+      <c r="A26" s="175"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="191"/>
+      <c r="D26" s="175"/>
       <c r="E26" s="181"/>
-      <c r="F26" s="171"/>
+      <c r="F26" s="175"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
       <c r="I26" s="18"/>
@@ -6324,17 +6324,17 @@
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
       <c r="O26" s="18"/>
-      <c r="P26" s="171"/>
-      <c r="Q26" s="171"/>
-      <c r="R26" s="187"/>
+      <c r="P26" s="175"/>
+      <c r="Q26" s="175"/>
+      <c r="R26" s="174"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="171"/>
-      <c r="B27" s="171"/>
-      <c r="C27" s="175"/>
-      <c r="D27" s="171"/>
+      <c r="A27" s="175"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="191"/>
+      <c r="D27" s="175"/>
       <c r="E27" s="181"/>
-      <c r="F27" s="171"/>
+      <c r="F27" s="175"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="18"/>
@@ -6344,17 +6344,17 @@
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
       <c r="O27" s="18"/>
-      <c r="P27" s="171"/>
-      <c r="Q27" s="171"/>
-      <c r="R27" s="187"/>
+      <c r="P27" s="175"/>
+      <c r="Q27" s="175"/>
+      <c r="R27" s="174"/>
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="171"/>
-      <c r="B28" s="171"/>
-      <c r="C28" s="175"/>
-      <c r="D28" s="171"/>
+      <c r="A28" s="175"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="191"/>
+      <c r="D28" s="175"/>
       <c r="E28" s="181"/>
-      <c r="F28" s="171"/>
+      <c r="F28" s="175"/>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="18"/>
@@ -6364,17 +6364,17 @@
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="18"/>
-      <c r="P28" s="171"/>
-      <c r="Q28" s="171"/>
-      <c r="R28" s="187"/>
+      <c r="P28" s="175"/>
+      <c r="Q28" s="175"/>
+      <c r="R28" s="174"/>
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="171"/>
-      <c r="B29" s="171"/>
-      <c r="C29" s="175"/>
-      <c r="D29" s="171"/>
+      <c r="A29" s="175"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="191"/>
+      <c r="D29" s="175"/>
       <c r="E29" s="181"/>
-      <c r="F29" s="171"/>
+      <c r="F29" s="175"/>
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
       <c r="I29" s="18"/>
@@ -6384,17 +6384,17 @@
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
       <c r="O29" s="18"/>
-      <c r="P29" s="171"/>
-      <c r="Q29" s="171"/>
-      <c r="R29" s="187"/>
+      <c r="P29" s="175"/>
+      <c r="Q29" s="175"/>
+      <c r="R29" s="174"/>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="171"/>
-      <c r="B30" s="171"/>
-      <c r="C30" s="175"/>
-      <c r="D30" s="171"/>
+      <c r="A30" s="175"/>
+      <c r="B30" s="175"/>
+      <c r="C30" s="191"/>
+      <c r="D30" s="175"/>
       <c r="E30" s="181"/>
-      <c r="F30" s="171"/>
+      <c r="F30" s="175"/>
       <c r="G30" s="17"/>
       <c r="H30" s="17"/>
       <c r="I30" s="18"/>
@@ -6404,17 +6404,17 @@
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
       <c r="O30" s="18"/>
-      <c r="P30" s="171"/>
-      <c r="Q30" s="171"/>
-      <c r="R30" s="187"/>
+      <c r="P30" s="175"/>
+      <c r="Q30" s="175"/>
+      <c r="R30" s="174"/>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="171"/>
-      <c r="B31" s="171"/>
-      <c r="C31" s="175"/>
-      <c r="D31" s="171"/>
+      <c r="A31" s="175"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="191"/>
+      <c r="D31" s="175"/>
       <c r="E31" s="181"/>
-      <c r="F31" s="171"/>
+      <c r="F31" s="175"/>
       <c r="G31" s="17"/>
       <c r="H31" s="17"/>
       <c r="I31" s="18"/>
@@ -6424,17 +6424,17 @@
       <c r="M31" s="18"/>
       <c r="N31" s="18"/>
       <c r="O31" s="18"/>
-      <c r="P31" s="171"/>
-      <c r="Q31" s="171"/>
-      <c r="R31" s="187"/>
+      <c r="P31" s="175"/>
+      <c r="Q31" s="175"/>
+      <c r="R31" s="174"/>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="171"/>
-      <c r="B32" s="171"/>
-      <c r="C32" s="175"/>
-      <c r="D32" s="171"/>
+      <c r="A32" s="175"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="191"/>
+      <c r="D32" s="175"/>
       <c r="E32" s="181"/>
-      <c r="F32" s="171"/>
+      <c r="F32" s="175"/>
       <c r="G32" s="17"/>
       <c r="H32" s="17"/>
       <c r="I32" s="18"/>
@@ -6444,17 +6444,17 @@
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
       <c r="O32" s="18"/>
-      <c r="P32" s="171"/>
-      <c r="Q32" s="171"/>
-      <c r="R32" s="187"/>
+      <c r="P32" s="175"/>
+      <c r="Q32" s="175"/>
+      <c r="R32" s="174"/>
     </row>
     <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="171"/>
-      <c r="B33" s="171"/>
-      <c r="C33" s="175"/>
-      <c r="D33" s="171"/>
+      <c r="A33" s="175"/>
+      <c r="B33" s="175"/>
+      <c r="C33" s="191"/>
+      <c r="D33" s="175"/>
       <c r="E33" s="181"/>
-      <c r="F33" s="171"/>
+      <c r="F33" s="175"/>
       <c r="G33" s="17"/>
       <c r="H33" s="17"/>
       <c r="I33" s="18"/>
@@ -6464,17 +6464,17 @@
       <c r="M33" s="18"/>
       <c r="N33" s="18"/>
       <c r="O33" s="18"/>
-      <c r="P33" s="171"/>
-      <c r="Q33" s="171"/>
-      <c r="R33" s="187"/>
+      <c r="P33" s="175"/>
+      <c r="Q33" s="175"/>
+      <c r="R33" s="174"/>
     </row>
     <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="171"/>
-      <c r="B34" s="171"/>
-      <c r="C34" s="175"/>
-      <c r="D34" s="171"/>
+      <c r="A34" s="175"/>
+      <c r="B34" s="175"/>
+      <c r="C34" s="191"/>
+      <c r="D34" s="175"/>
       <c r="E34" s="181"/>
-      <c r="F34" s="171"/>
+      <c r="F34" s="175"/>
       <c r="G34" s="17"/>
       <c r="H34" s="17"/>
       <c r="I34" s="18"/>
@@ -6484,16 +6484,16 @@
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
       <c r="O34" s="18"/>
-      <c r="P34" s="171"/>
-      <c r="Q34" s="171"/>
-      <c r="R34" s="187"/>
+      <c r="P34" s="175"/>
+      <c r="Q34" s="175"/>
+      <c r="R34" s="174"/>
     </row>
     <row r="35" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="171"/>
-      <c r="B35" s="171"/>
-      <c r="C35" s="179"/>
+      <c r="A35" s="175"/>
+      <c r="B35" s="175"/>
+      <c r="C35" s="194"/>
       <c r="D35" s="169"/>
-      <c r="E35" s="167"/>
+      <c r="E35" s="171"/>
       <c r="F35" s="169"/>
       <c r="G35" s="17"/>
       <c r="H35" s="17"/>
@@ -6504,13 +6504,13 @@
       <c r="M35" s="18"/>
       <c r="N35" s="18"/>
       <c r="O35" s="18"/>
-      <c r="P35" s="171"/>
+      <c r="P35" s="175"/>
       <c r="Q35" s="169"/>
-      <c r="R35" s="187"/>
+      <c r="R35" s="174"/>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="171"/>
-      <c r="B36" s="171"/>
+      <c r="A36" s="175"/>
+      <c r="B36" s="175"/>
       <c r="C36" s="97" t="s">
         <v>9</v>
       </c>
@@ -6532,13 +6532,13 @@
       <c r="M36" s="17"/>
       <c r="N36" s="17"/>
       <c r="O36" s="17"/>
-      <c r="P36" s="171"/>
+      <c r="P36" s="175"/>
       <c r="Q36" s="151"/>
-      <c r="R36" s="187"/>
+      <c r="R36" s="174"/>
     </row>
     <row r="37" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="171"/>
-      <c r="B37" s="171"/>
+      <c r="A37" s="175"/>
+      <c r="B37" s="175"/>
       <c r="C37" s="31" t="s">
         <v>13</v>
       </c>
@@ -6560,15 +6560,15 @@
       <c r="M37" s="17"/>
       <c r="N37" s="17"/>
       <c r="O37" s="17"/>
-      <c r="P37" s="171"/>
+      <c r="P37" s="175"/>
       <c r="Q37" s="52">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R37" s="187"/>
+      <c r="R37" s="174"/>
     </row>
     <row r="38" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="171"/>
-      <c r="B38" s="171"/>
+      <c r="A38" s="175"/>
+      <c r="B38" s="175"/>
       <c r="C38" s="96" t="s">
         <v>14</v>
       </c>
@@ -6608,13 +6608,13 @@
       <c r="O38" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="P38" s="171"/>
+      <c r="P38" s="175"/>
       <c r="Q38" s="153"/>
-      <c r="R38" s="187"/>
+      <c r="R38" s="174"/>
     </row>
     <row r="39" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="171"/>
-      <c r="B39" s="171"/>
+      <c r="A39" s="175"/>
+      <c r="B39" s="175"/>
       <c r="C39" s="32" t="s">
         <v>27</v>
       </c>
@@ -6654,15 +6654,15 @@
       <c r="O39" s="4">
         <v>0.33329999999999999</v>
       </c>
-      <c r="P39" s="171"/>
+      <c r="P39" s="175"/>
       <c r="Q39" s="52">
         <v>0.66669999999999996</v>
       </c>
-      <c r="R39" s="187"/>
+      <c r="R39" s="174"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A40" s="171"/>
-      <c r="B40" s="171"/>
+      <c r="A40" s="175"/>
+      <c r="B40" s="175"/>
       <c r="C40" s="98" t="s">
         <v>28</v>
       </c>
@@ -6684,20 +6684,20 @@
       <c r="M40" s="21"/>
       <c r="N40" s="21"/>
       <c r="O40" s="21"/>
-      <c r="P40" s="171"/>
+      <c r="P40" s="175"/>
       <c r="Q40" s="153"/>
-      <c r="R40" s="187"/>
+      <c r="R40" s="174"/>
     </row>
     <row r="41" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="171"/>
-      <c r="B41" s="171"/>
+      <c r="A41" s="175"/>
+      <c r="B41" s="175"/>
       <c r="C41" s="33" t="s">
         <v>32</v>
       </c>
       <c r="D41" s="168">
         <v>1</v>
       </c>
-      <c r="E41" s="166">
+      <c r="E41" s="172">
         <v>0.66659999999999997</v>
       </c>
       <c r="F41" s="168">
@@ -6712,18 +6712,18 @@
       <c r="M41" s="21"/>
       <c r="N41" s="21"/>
       <c r="O41" s="21"/>
-      <c r="P41" s="171"/>
-      <c r="Q41" s="166">
+      <c r="P41" s="175"/>
+      <c r="Q41" s="172">
         <v>1</v>
       </c>
-      <c r="R41" s="187"/>
+      <c r="R41" s="174"/>
     </row>
     <row r="42" spans="1:18" ht="207.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="171"/>
+      <c r="A42" s="175"/>
       <c r="B42" s="169"/>
       <c r="C42" s="13"/>
       <c r="D42" s="169"/>
-      <c r="E42" s="167"/>
+      <c r="E42" s="171"/>
       <c r="F42" s="169"/>
       <c r="G42" s="17"/>
       <c r="H42" s="18"/>
@@ -6734,12 +6734,12 @@
       <c r="M42" s="18"/>
       <c r="N42" s="18"/>
       <c r="O42" s="18"/>
-      <c r="P42" s="171"/>
-      <c r="Q42" s="167"/>
-      <c r="R42" s="187"/>
+      <c r="P42" s="175"/>
+      <c r="Q42" s="171"/>
+      <c r="R42" s="174"/>
     </row>
     <row r="43" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="171"/>
+      <c r="A43" s="175"/>
       <c r="B43" s="90"/>
       <c r="C43" s="93"/>
       <c r="D43" s="94"/>
@@ -6756,16 +6756,16 @@
       <c r="O43" s="159" t="s">
         <v>33</v>
       </c>
-      <c r="P43" s="171"/>
+      <c r="P43" s="175"/>
       <c r="Q43" s="157">
         <f>(Q3+Q20+Q37+Q39+Q41)/5</f>
         <v>0.59997999999999996</v>
       </c>
-      <c r="R43" s="187"/>
+      <c r="R43" s="174"/>
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="171"/>
-      <c r="B44" s="184" t="s">
+      <c r="A44" s="175"/>
+      <c r="B44" s="183" t="s">
         <v>34</v>
       </c>
       <c r="C44" s="99" t="s">
@@ -6793,20 +6793,20 @@
       <c r="M44" s="22"/>
       <c r="N44" s="22"/>
       <c r="O44" s="22"/>
-      <c r="P44" s="171"/>
+      <c r="P44" s="175"/>
       <c r="Q44" s="153"/>
-      <c r="R44" s="187"/>
+      <c r="R44" s="174"/>
     </row>
     <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="171"/>
-      <c r="B45" s="171"/>
+      <c r="A45" s="175"/>
+      <c r="B45" s="175"/>
       <c r="C45" s="33" t="s">
         <v>41</v>
       </c>
       <c r="D45" s="168">
         <v>0.4</v>
       </c>
-      <c r="E45" s="166">
+      <c r="E45" s="172">
         <v>0.8</v>
       </c>
       <c r="F45" s="168">
@@ -6825,18 +6825,18 @@
       <c r="M45" s="22"/>
       <c r="N45" s="22"/>
       <c r="O45" s="22"/>
-      <c r="P45" s="171"/>
-      <c r="Q45" s="166">
+      <c r="P45" s="175"/>
+      <c r="Q45" s="172">
         <v>0.8</v>
       </c>
-      <c r="R45" s="187"/>
+      <c r="R45" s="174"/>
     </row>
     <row r="46" spans="1:18" ht="176.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="171"/>
-      <c r="B46" s="171"/>
+      <c r="A46" s="175"/>
+      <c r="B46" s="175"/>
       <c r="C46" s="34"/>
       <c r="D46" s="169"/>
-      <c r="E46" s="167"/>
+      <c r="E46" s="171"/>
       <c r="F46" s="169"/>
       <c r="G46" s="169"/>
       <c r="H46" s="169"/>
@@ -6847,13 +6847,13 @@
       <c r="M46" s="22"/>
       <c r="N46" s="22"/>
       <c r="O46" s="22"/>
-      <c r="P46" s="171"/>
-      <c r="Q46" s="167"/>
-      <c r="R46" s="187"/>
+      <c r="P46" s="175"/>
+      <c r="Q46" s="171"/>
+      <c r="R46" s="174"/>
     </row>
     <row r="47" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="171"/>
-      <c r="B47" s="171"/>
+      <c r="A47" s="175"/>
+      <c r="B47" s="175"/>
       <c r="C47" s="100" t="s">
         <v>42</v>
       </c>
@@ -6879,20 +6879,20 @@
       <c r="M47" s="22"/>
       <c r="N47" s="22"/>
       <c r="O47" s="22"/>
-      <c r="P47" s="171"/>
+      <c r="P47" s="175"/>
       <c r="Q47" s="153"/>
-      <c r="R47" s="187"/>
+      <c r="R47" s="174"/>
     </row>
     <row r="48" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="171"/>
-      <c r="B48" s="171"/>
+      <c r="A48" s="175"/>
+      <c r="B48" s="175"/>
       <c r="C48" s="33" t="s">
         <v>48</v>
       </c>
       <c r="D48" s="168">
         <v>0.2</v>
       </c>
-      <c r="E48" s="166">
+      <c r="E48" s="172">
         <v>0.4</v>
       </c>
       <c r="F48" s="168">
@@ -6911,18 +6911,18 @@
       <c r="M48" s="22"/>
       <c r="N48" s="22"/>
       <c r="O48" s="22"/>
-      <c r="P48" s="171"/>
-      <c r="Q48" s="166">
+      <c r="P48" s="175"/>
+      <c r="Q48" s="172">
         <v>0.4</v>
       </c>
-      <c r="R48" s="187"/>
+      <c r="R48" s="174"/>
     </row>
     <row r="49" spans="1:18" ht="167.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="171"/>
-      <c r="B49" s="171"/>
+      <c r="A49" s="175"/>
+      <c r="B49" s="175"/>
       <c r="C49" s="12"/>
       <c r="D49" s="169"/>
-      <c r="E49" s="167"/>
+      <c r="E49" s="171"/>
       <c r="F49" s="169"/>
       <c r="G49" s="169"/>
       <c r="H49" s="169"/>
@@ -6933,12 +6933,12 @@
       <c r="M49" s="22"/>
       <c r="N49" s="22"/>
       <c r="O49" s="22"/>
-      <c r="P49" s="171"/>
-      <c r="Q49" s="167"/>
-      <c r="R49" s="187"/>
+      <c r="P49" s="175"/>
+      <c r="Q49" s="171"/>
+      <c r="R49" s="174"/>
     </row>
     <row r="50" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="171"/>
+      <c r="A50" s="175"/>
       <c r="B50" s="90"/>
       <c r="C50" s="93"/>
       <c r="D50" s="94"/>
@@ -6950,21 +6950,21 @@
       <c r="J50" s="85"/>
       <c r="K50" s="85"/>
       <c r="L50" s="85"/>
-      <c r="M50" s="195" t="s">
+      <c r="M50" s="177" t="s">
         <v>49</v>
       </c>
-      <c r="N50" s="196"/>
-      <c r="O50" s="197"/>
-      <c r="P50" s="171"/>
+      <c r="N50" s="178"/>
+      <c r="O50" s="179"/>
+      <c r="P50" s="175"/>
       <c r="Q50" s="157">
         <f>(Q45+Q48)/2</f>
         <v>0.60000000000000009</v>
       </c>
-      <c r="R50" s="187"/>
+      <c r="R50" s="174"/>
     </row>
     <row r="51" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="171"/>
-      <c r="B51" s="185" t="s">
+      <c r="A51" s="175"/>
+      <c r="B51" s="184" t="s">
         <v>50</v>
       </c>
       <c r="C51" s="99" t="s">
@@ -6990,26 +6990,26 @@
       <c r="M51" s="22"/>
       <c r="N51" s="22"/>
       <c r="O51" s="22"/>
-      <c r="P51" s="171"/>
+      <c r="P51" s="175"/>
       <c r="Q51" s="139"/>
-      <c r="R51" s="187"/>
+      <c r="R51" s="174"/>
     </row>
     <row r="52" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="171"/>
-      <c r="B52" s="171"/>
+      <c r="A52" s="175"/>
+      <c r="B52" s="175"/>
       <c r="C52" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D52" s="170">
+      <c r="D52" s="176">
         <v>1</v>
       </c>
-      <c r="E52" s="170">
+      <c r="E52" s="176">
         <v>0.5</v>
       </c>
-      <c r="F52" s="170">
+      <c r="F52" s="176">
         <v>0.75</v>
       </c>
-      <c r="G52" s="170">
+      <c r="G52" s="176">
         <v>0.25</v>
       </c>
       <c r="H52" s="22"/>
@@ -7020,20 +7020,20 @@
       <c r="M52" s="22"/>
       <c r="N52" s="22"/>
       <c r="O52" s="22"/>
-      <c r="P52" s="171"/>
+      <c r="P52" s="175"/>
       <c r="Q52" s="168">
         <v>0.5</v>
       </c>
-      <c r="R52" s="187"/>
+      <c r="R52" s="174"/>
     </row>
     <row r="53" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="171"/>
-      <c r="B53" s="171"/>
-      <c r="C53" s="191"/>
-      <c r="D53" s="171"/>
-      <c r="E53" s="171"/>
-      <c r="F53" s="171"/>
-      <c r="G53" s="171"/>
+      <c r="A53" s="175"/>
+      <c r="B53" s="175"/>
+      <c r="C53" s="188"/>
+      <c r="D53" s="175"/>
+      <c r="E53" s="175"/>
+      <c r="F53" s="175"/>
+      <c r="G53" s="175"/>
       <c r="H53" s="22"/>
       <c r="I53" s="22"/>
       <c r="J53" s="22"/>
@@ -7042,18 +7042,18 @@
       <c r="M53" s="22"/>
       <c r="N53" s="22"/>
       <c r="O53" s="22"/>
-      <c r="P53" s="171"/>
-      <c r="Q53" s="171"/>
-      <c r="R53" s="187"/>
+      <c r="P53" s="175"/>
+      <c r="Q53" s="175"/>
+      <c r="R53" s="174"/>
     </row>
     <row r="54" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="171"/>
-      <c r="B54" s="171"/>
-      <c r="C54" s="171"/>
-      <c r="D54" s="171"/>
-      <c r="E54" s="171"/>
-      <c r="F54" s="171"/>
-      <c r="G54" s="171"/>
+      <c r="A54" s="175"/>
+      <c r="B54" s="175"/>
+      <c r="C54" s="175"/>
+      <c r="D54" s="175"/>
+      <c r="E54" s="175"/>
+      <c r="F54" s="175"/>
+      <c r="G54" s="175"/>
       <c r="H54" s="22"/>
       <c r="I54" s="22"/>
       <c r="J54" s="22"/>
@@ -7062,18 +7062,18 @@
       <c r="M54" s="22"/>
       <c r="N54" s="22"/>
       <c r="O54" s="22"/>
-      <c r="P54" s="171"/>
-      <c r="Q54" s="171"/>
-      <c r="R54" s="187"/>
+      <c r="P54" s="175"/>
+      <c r="Q54" s="175"/>
+      <c r="R54" s="174"/>
     </row>
     <row r="55" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="171"/>
-      <c r="B55" s="171"/>
-      <c r="C55" s="171"/>
-      <c r="D55" s="171"/>
-      <c r="E55" s="171"/>
-      <c r="F55" s="171"/>
-      <c r="G55" s="171"/>
+      <c r="A55" s="175"/>
+      <c r="B55" s="175"/>
+      <c r="C55" s="175"/>
+      <c r="D55" s="175"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="175"/>
+      <c r="G55" s="175"/>
       <c r="H55" s="22"/>
       <c r="I55" s="22"/>
       <c r="J55" s="22"/>
@@ -7082,18 +7082,18 @@
       <c r="M55" s="22"/>
       <c r="N55" s="22"/>
       <c r="O55" s="22"/>
-      <c r="P55" s="171"/>
-      <c r="Q55" s="171"/>
-      <c r="R55" s="187"/>
+      <c r="P55" s="175"/>
+      <c r="Q55" s="175"/>
+      <c r="R55" s="174"/>
     </row>
     <row r="56" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="171"/>
-      <c r="B56" s="171"/>
-      <c r="C56" s="171"/>
-      <c r="D56" s="171"/>
-      <c r="E56" s="171"/>
-      <c r="F56" s="171"/>
-      <c r="G56" s="171"/>
+      <c r="A56" s="175"/>
+      <c r="B56" s="175"/>
+      <c r="C56" s="175"/>
+      <c r="D56" s="175"/>
+      <c r="E56" s="175"/>
+      <c r="F56" s="175"/>
+      <c r="G56" s="175"/>
       <c r="H56" s="22"/>
       <c r="I56" s="22"/>
       <c r="J56" s="22"/>
@@ -7102,18 +7102,18 @@
       <c r="M56" s="22"/>
       <c r="N56" s="22"/>
       <c r="O56" s="22"/>
-      <c r="P56" s="171"/>
-      <c r="Q56" s="171"/>
-      <c r="R56" s="187"/>
+      <c r="P56" s="175"/>
+      <c r="Q56" s="175"/>
+      <c r="R56" s="174"/>
     </row>
     <row r="57" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="171"/>
-      <c r="B57" s="171"/>
-      <c r="C57" s="171"/>
-      <c r="D57" s="171"/>
-      <c r="E57" s="171"/>
-      <c r="F57" s="171"/>
-      <c r="G57" s="171"/>
+      <c r="A57" s="175"/>
+      <c r="B57" s="175"/>
+      <c r="C57" s="175"/>
+      <c r="D57" s="175"/>
+      <c r="E57" s="175"/>
+      <c r="F57" s="175"/>
+      <c r="G57" s="175"/>
       <c r="H57" s="22"/>
       <c r="I57" s="22"/>
       <c r="J57" s="22"/>
@@ -7122,18 +7122,18 @@
       <c r="M57" s="22"/>
       <c r="N57" s="22"/>
       <c r="O57" s="22"/>
-      <c r="P57" s="171"/>
-      <c r="Q57" s="171"/>
-      <c r="R57" s="187"/>
+      <c r="P57" s="175"/>
+      <c r="Q57" s="175"/>
+      <c r="R57" s="174"/>
     </row>
     <row r="58" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="171"/>
-      <c r="B58" s="171"/>
-      <c r="C58" s="171"/>
-      <c r="D58" s="171"/>
-      <c r="E58" s="171"/>
-      <c r="F58" s="171"/>
-      <c r="G58" s="171"/>
+      <c r="A58" s="175"/>
+      <c r="B58" s="175"/>
+      <c r="C58" s="175"/>
+      <c r="D58" s="175"/>
+      <c r="E58" s="175"/>
+      <c r="F58" s="175"/>
+      <c r="G58" s="175"/>
       <c r="H58" s="22"/>
       <c r="I58" s="22"/>
       <c r="J58" s="22"/>
@@ -7142,18 +7142,18 @@
       <c r="M58" s="22"/>
       <c r="N58" s="22"/>
       <c r="O58" s="22"/>
-      <c r="P58" s="171"/>
-      <c r="Q58" s="171"/>
-      <c r="R58" s="187"/>
+      <c r="P58" s="175"/>
+      <c r="Q58" s="175"/>
+      <c r="R58" s="174"/>
     </row>
     <row r="59" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="171"/>
-      <c r="B59" s="171"/>
-      <c r="C59" s="171"/>
-      <c r="D59" s="171"/>
-      <c r="E59" s="171"/>
-      <c r="F59" s="171"/>
-      <c r="G59" s="171"/>
+      <c r="A59" s="175"/>
+      <c r="B59" s="175"/>
+      <c r="C59" s="175"/>
+      <c r="D59" s="175"/>
+      <c r="E59" s="175"/>
+      <c r="F59" s="175"/>
+      <c r="G59" s="175"/>
       <c r="H59" s="22"/>
       <c r="I59" s="22"/>
       <c r="J59" s="22"/>
@@ -7162,18 +7162,18 @@
       <c r="M59" s="22"/>
       <c r="N59" s="22"/>
       <c r="O59" s="22"/>
-      <c r="P59" s="171"/>
-      <c r="Q59" s="171"/>
-      <c r="R59" s="187"/>
+      <c r="P59" s="175"/>
+      <c r="Q59" s="175"/>
+      <c r="R59" s="174"/>
     </row>
     <row r="60" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="171"/>
-      <c r="B60" s="171"/>
-      <c r="C60" s="171"/>
-      <c r="D60" s="171"/>
-      <c r="E60" s="171"/>
-      <c r="F60" s="171"/>
-      <c r="G60" s="171"/>
+      <c r="A60" s="175"/>
+      <c r="B60" s="175"/>
+      <c r="C60" s="175"/>
+      <c r="D60" s="175"/>
+      <c r="E60" s="175"/>
+      <c r="F60" s="175"/>
+      <c r="G60" s="175"/>
       <c r="H60" s="22"/>
       <c r="I60" s="22"/>
       <c r="J60" s="22"/>
@@ -7182,18 +7182,18 @@
       <c r="M60" s="22"/>
       <c r="N60" s="22"/>
       <c r="O60" s="22"/>
-      <c r="P60" s="171"/>
-      <c r="Q60" s="171"/>
-      <c r="R60" s="187"/>
+      <c r="P60" s="175"/>
+      <c r="Q60" s="175"/>
+      <c r="R60" s="174"/>
     </row>
     <row r="61" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="171"/>
-      <c r="B61" s="171"/>
-      <c r="C61" s="171"/>
-      <c r="D61" s="171"/>
-      <c r="E61" s="171"/>
-      <c r="F61" s="171"/>
-      <c r="G61" s="171"/>
+      <c r="A61" s="175"/>
+      <c r="B61" s="175"/>
+      <c r="C61" s="175"/>
+      <c r="D61" s="175"/>
+      <c r="E61" s="175"/>
+      <c r="F61" s="175"/>
+      <c r="G61" s="175"/>
       <c r="H61" s="22"/>
       <c r="I61" s="22"/>
       <c r="J61" s="22"/>
@@ -7202,18 +7202,18 @@
       <c r="M61" s="22"/>
       <c r="N61" s="22"/>
       <c r="O61" s="22"/>
-      <c r="P61" s="171"/>
-      <c r="Q61" s="171"/>
-      <c r="R61" s="187"/>
+      <c r="P61" s="175"/>
+      <c r="Q61" s="175"/>
+      <c r="R61" s="174"/>
     </row>
     <row r="62" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="171"/>
-      <c r="B62" s="171"/>
-      <c r="C62" s="171"/>
-      <c r="D62" s="171"/>
-      <c r="E62" s="171"/>
-      <c r="F62" s="171"/>
-      <c r="G62" s="171"/>
+      <c r="A62" s="175"/>
+      <c r="B62" s="175"/>
+      <c r="C62" s="175"/>
+      <c r="D62" s="175"/>
+      <c r="E62" s="175"/>
+      <c r="F62" s="175"/>
+      <c r="G62" s="175"/>
       <c r="H62" s="22"/>
       <c r="I62" s="22"/>
       <c r="J62" s="22"/>
@@ -7222,18 +7222,18 @@
       <c r="M62" s="22"/>
       <c r="N62" s="22"/>
       <c r="O62" s="22"/>
-      <c r="P62" s="171"/>
-      <c r="Q62" s="171"/>
-      <c r="R62" s="187"/>
+      <c r="P62" s="175"/>
+      <c r="Q62" s="175"/>
+      <c r="R62" s="174"/>
     </row>
     <row r="63" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="171"/>
-      <c r="B63" s="171"/>
-      <c r="C63" s="171"/>
-      <c r="D63" s="171"/>
-      <c r="E63" s="171"/>
-      <c r="F63" s="171"/>
-      <c r="G63" s="171"/>
+      <c r="A63" s="175"/>
+      <c r="B63" s="175"/>
+      <c r="C63" s="175"/>
+      <c r="D63" s="175"/>
+      <c r="E63" s="175"/>
+      <c r="F63" s="175"/>
+      <c r="G63" s="175"/>
       <c r="H63" s="22"/>
       <c r="I63" s="22"/>
       <c r="J63" s="22"/>
@@ -7242,18 +7242,18 @@
       <c r="M63" s="22"/>
       <c r="N63" s="22"/>
       <c r="O63" s="22"/>
-      <c r="P63" s="171"/>
-      <c r="Q63" s="171"/>
-      <c r="R63" s="187"/>
+      <c r="P63" s="175"/>
+      <c r="Q63" s="175"/>
+      <c r="R63" s="174"/>
     </row>
     <row r="64" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="171"/>
-      <c r="B64" s="171"/>
-      <c r="C64" s="171"/>
-      <c r="D64" s="171"/>
-      <c r="E64" s="171"/>
-      <c r="F64" s="171"/>
-      <c r="G64" s="171"/>
+      <c r="A64" s="175"/>
+      <c r="B64" s="175"/>
+      <c r="C64" s="175"/>
+      <c r="D64" s="175"/>
+      <c r="E64" s="175"/>
+      <c r="F64" s="175"/>
+      <c r="G64" s="175"/>
       <c r="H64" s="22"/>
       <c r="I64" s="22"/>
       <c r="J64" s="22"/>
@@ -7262,18 +7262,18 @@
       <c r="M64" s="22"/>
       <c r="N64" s="22"/>
       <c r="O64" s="22"/>
-      <c r="P64" s="171"/>
-      <c r="Q64" s="171"/>
-      <c r="R64" s="187"/>
+      <c r="P64" s="175"/>
+      <c r="Q64" s="175"/>
+      <c r="R64" s="174"/>
     </row>
     <row r="65" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="171"/>
-      <c r="B65" s="171"/>
-      <c r="C65" s="171"/>
-      <c r="D65" s="171"/>
-      <c r="E65" s="171"/>
-      <c r="F65" s="171"/>
-      <c r="G65" s="171"/>
+      <c r="A65" s="175"/>
+      <c r="B65" s="175"/>
+      <c r="C65" s="175"/>
+      <c r="D65" s="175"/>
+      <c r="E65" s="175"/>
+      <c r="F65" s="175"/>
+      <c r="G65" s="175"/>
       <c r="H65" s="22"/>
       <c r="I65" s="22"/>
       <c r="J65" s="22"/>
@@ -7282,13 +7282,13 @@
       <c r="M65" s="22"/>
       <c r="N65" s="22"/>
       <c r="O65" s="22"/>
-      <c r="P65" s="171"/>
-      <c r="Q65" s="171"/>
-      <c r="R65" s="187"/>
+      <c r="P65" s="175"/>
+      <c r="Q65" s="175"/>
+      <c r="R65" s="174"/>
     </row>
     <row r="66" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="171"/>
-      <c r="B66" s="171"/>
+      <c r="A66" s="175"/>
+      <c r="B66" s="175"/>
       <c r="C66" s="169"/>
       <c r="D66" s="169"/>
       <c r="E66" s="169"/>
@@ -7302,13 +7302,13 @@
       <c r="M66" s="22"/>
       <c r="N66" s="22"/>
       <c r="O66" s="22"/>
-      <c r="P66" s="171"/>
+      <c r="P66" s="175"/>
       <c r="Q66" s="169"/>
-      <c r="R66" s="187"/>
+      <c r="R66" s="174"/>
     </row>
     <row r="67" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="171"/>
-      <c r="B67" s="171"/>
+      <c r="A67" s="175"/>
+      <c r="B67" s="175"/>
       <c r="C67" s="100" t="s">
         <v>57</v>
       </c>
@@ -7334,13 +7334,13 @@
       <c r="M67" s="22"/>
       <c r="N67" s="22"/>
       <c r="O67" s="22"/>
-      <c r="P67" s="171"/>
+      <c r="P67" s="175"/>
       <c r="Q67" s="153"/>
-      <c r="R67" s="187"/>
+      <c r="R67" s="174"/>
     </row>
     <row r="68" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="171"/>
-      <c r="B68" s="171"/>
+      <c r="A68" s="175"/>
+      <c r="B68" s="175"/>
       <c r="C68" s="30" t="s">
         <v>63</v>
       </c>
@@ -7366,15 +7366,15 @@
       <c r="M68" s="22"/>
       <c r="N68" s="22"/>
       <c r="O68" s="22"/>
-      <c r="P68" s="171"/>
+      <c r="P68" s="175"/>
       <c r="Q68" s="52">
         <v>0.4</v>
       </c>
-      <c r="R68" s="187"/>
+      <c r="R68" s="174"/>
     </row>
     <row r="69" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="171"/>
-      <c r="B69" s="171"/>
+      <c r="A69" s="175"/>
+      <c r="B69" s="175"/>
       <c r="C69" s="96" t="s">
         <v>64</v>
       </c>
@@ -7396,23 +7396,23 @@
       <c r="M69" s="22"/>
       <c r="N69" s="22"/>
       <c r="O69" s="22"/>
-      <c r="P69" s="171"/>
+      <c r="P69" s="175"/>
       <c r="Q69" s="153"/>
-      <c r="R69" s="187"/>
+      <c r="R69" s="174"/>
     </row>
     <row r="70" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="171"/>
-      <c r="B70" s="171"/>
+      <c r="A70" s="175"/>
+      <c r="B70" s="175"/>
       <c r="C70" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="D70" s="170">
+      <c r="D70" s="176">
         <v>0.33329999999999999</v>
       </c>
-      <c r="E70" s="172">
+      <c r="E70" s="170">
         <v>0.66659999999999997</v>
       </c>
-      <c r="F70" s="170">
+      <c r="F70" s="176">
         <v>1</v>
       </c>
       <c r="G70" s="22"/>
@@ -7424,18 +7424,18 @@
       <c r="M70" s="22"/>
       <c r="N70" s="22"/>
       <c r="O70" s="22"/>
-      <c r="P70" s="171"/>
-      <c r="Q70" s="166">
+      <c r="P70" s="175"/>
+      <c r="Q70" s="172">
         <v>1</v>
       </c>
-      <c r="R70" s="187"/>
+      <c r="R70" s="174"/>
     </row>
     <row r="71" spans="1:18" ht="205.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="171"/>
+      <c r="A71" s="175"/>
       <c r="B71" s="169"/>
       <c r="C71" s="12"/>
       <c r="D71" s="169"/>
-      <c r="E71" s="167"/>
+      <c r="E71" s="171"/>
       <c r="F71" s="169"/>
       <c r="G71" s="22"/>
       <c r="H71" s="22"/>
@@ -7446,12 +7446,12 @@
       <c r="M71" s="22"/>
       <c r="N71" s="22"/>
       <c r="O71" s="22"/>
-      <c r="P71" s="171"/>
-      <c r="Q71" s="167"/>
-      <c r="R71" s="187"/>
+      <c r="P71" s="175"/>
+      <c r="Q71" s="171"/>
+      <c r="R71" s="174"/>
     </row>
     <row r="72" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="171"/>
+      <c r="A72" s="175"/>
       <c r="B72" s="90"/>
       <c r="C72" s="93"/>
       <c r="D72" s="94"/>
@@ -7468,16 +7468,16 @@
       <c r="O72" s="160" t="s">
         <v>69</v>
       </c>
-      <c r="P72" s="171"/>
+      <c r="P72" s="175"/>
       <c r="Q72" s="157">
         <f>(Q52+Q68+Q70)/3</f>
         <v>0.6333333333333333</v>
       </c>
-      <c r="R72" s="187"/>
+      <c r="R72" s="174"/>
     </row>
     <row r="73" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="171"/>
-      <c r="B73" s="188" t="s">
+      <c r="A73" s="175"/>
+      <c r="B73" s="186" t="s">
         <v>70</v>
       </c>
       <c r="C73" s="101" t="s">
@@ -7501,13 +7501,13 @@
       <c r="M73" s="22"/>
       <c r="N73" s="22"/>
       <c r="O73" s="22"/>
-      <c r="P73" s="171"/>
+      <c r="P73" s="175"/>
       <c r="Q73" s="154"/>
-      <c r="R73" s="187"/>
+      <c r="R73" s="174"/>
     </row>
     <row r="74" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="171"/>
-      <c r="B74" s="171"/>
+      <c r="A74" s="175"/>
+      <c r="B74" s="175"/>
       <c r="C74" s="37" t="s">
         <v>74</v>
       </c>
@@ -7529,15 +7529,15 @@
       <c r="M74" s="22"/>
       <c r="N74" s="22"/>
       <c r="O74" s="22"/>
-      <c r="P74" s="171"/>
+      <c r="P74" s="175"/>
       <c r="Q74" s="53">
         <v>0.33329999999999999</v>
       </c>
-      <c r="R74" s="187"/>
+      <c r="R74" s="174"/>
     </row>
     <row r="75" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="171"/>
-      <c r="B75" s="171"/>
+      <c r="A75" s="175"/>
+      <c r="B75" s="175"/>
       <c r="C75" s="102" t="s">
         <v>75</v>
       </c>
@@ -7563,13 +7563,13 @@
       <c r="M75" s="20"/>
       <c r="N75" s="20"/>
       <c r="O75" s="20"/>
-      <c r="P75" s="171"/>
+      <c r="P75" s="175"/>
       <c r="Q75" s="154"/>
-      <c r="R75" s="187"/>
+      <c r="R75" s="174"/>
     </row>
     <row r="76" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="171"/>
-      <c r="B76" s="171"/>
+      <c r="A76" s="175"/>
+      <c r="B76" s="175"/>
       <c r="C76" s="38" t="s">
         <v>81</v>
       </c>
@@ -7595,15 +7595,15 @@
       <c r="M76" s="20"/>
       <c r="N76" s="20"/>
       <c r="O76" s="20"/>
-      <c r="P76" s="171"/>
+      <c r="P76" s="175"/>
       <c r="Q76" s="51">
         <v>0.6</v>
       </c>
-      <c r="R76" s="187"/>
+      <c r="R76" s="174"/>
     </row>
     <row r="77" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="171"/>
-      <c r="B77" s="171"/>
+      <c r="A77" s="175"/>
+      <c r="B77" s="175"/>
       <c r="C77" s="102" t="s">
         <v>82</v>
       </c>
@@ -7629,13 +7629,13 @@
       <c r="M77" s="18"/>
       <c r="N77" s="18"/>
       <c r="O77" s="18"/>
-      <c r="P77" s="171"/>
+      <c r="P77" s="175"/>
       <c r="Q77" s="155"/>
-      <c r="R77" s="187"/>
+      <c r="R77" s="174"/>
     </row>
     <row r="78" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="171"/>
-      <c r="B78" s="171"/>
+      <c r="A78" s="175"/>
+      <c r="B78" s="175"/>
       <c r="C78" s="38" t="s">
         <v>88</v>
       </c>
@@ -7661,15 +7661,15 @@
       <c r="M78" s="18"/>
       <c r="N78" s="18"/>
       <c r="O78" s="18"/>
-      <c r="P78" s="171"/>
+      <c r="P78" s="175"/>
       <c r="Q78" s="62">
         <v>0.4</v>
       </c>
-      <c r="R78" s="187"/>
+      <c r="R78" s="174"/>
     </row>
     <row r="79" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="171"/>
-      <c r="B79" s="171"/>
+      <c r="A79" s="175"/>
+      <c r="B79" s="175"/>
       <c r="C79" s="103" t="s">
         <v>89</v>
       </c>
@@ -7691,13 +7691,13 @@
       <c r="M79" s="18"/>
       <c r="N79" s="18"/>
       <c r="O79" s="18"/>
-      <c r="P79" s="171"/>
+      <c r="P79" s="175"/>
       <c r="Q79" s="127"/>
-      <c r="R79" s="187"/>
+      <c r="R79" s="174"/>
     </row>
     <row r="80" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="171"/>
-      <c r="B80" s="171"/>
+      <c r="A80" s="175"/>
+      <c r="B80" s="175"/>
       <c r="C80" s="37" t="s">
         <v>93</v>
       </c>
@@ -7719,15 +7719,15 @@
       <c r="M80" s="18"/>
       <c r="N80" s="18"/>
       <c r="O80" s="18"/>
-      <c r="P80" s="171"/>
+      <c r="P80" s="175"/>
       <c r="Q80" s="53">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R80" s="187"/>
+      <c r="R80" s="174"/>
     </row>
     <row r="81" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="171"/>
-      <c r="B81" s="171"/>
+      <c r="A81" s="175"/>
+      <c r="B81" s="175"/>
       <c r="C81" s="102" t="s">
         <v>94</v>
       </c>
@@ -7749,13 +7749,13 @@
       <c r="M81" s="22"/>
       <c r="N81" s="22"/>
       <c r="O81" s="22"/>
-      <c r="P81" s="171"/>
+      <c r="P81" s="175"/>
       <c r="Q81" s="154"/>
-      <c r="R81" s="187"/>
+      <c r="R81" s="174"/>
     </row>
     <row r="82" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="171"/>
-      <c r="B82" s="171"/>
+      <c r="A82" s="175"/>
+      <c r="B82" s="175"/>
       <c r="C82" s="37" t="s">
         <v>98</v>
       </c>
@@ -7777,15 +7777,15 @@
       <c r="M82" s="22"/>
       <c r="N82" s="22"/>
       <c r="O82" s="22"/>
-      <c r="P82" s="171"/>
+      <c r="P82" s="175"/>
       <c r="Q82" s="53">
         <v>1</v>
       </c>
-      <c r="R82" s="187"/>
+      <c r="R82" s="174"/>
     </row>
     <row r="83" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="171"/>
-      <c r="B83" s="171"/>
+      <c r="A83" s="175"/>
+      <c r="B83" s="175"/>
       <c r="C83" s="102" t="s">
         <v>99</v>
       </c>
@@ -7805,13 +7805,13 @@
       <c r="M83" s="22"/>
       <c r="N83" s="22"/>
       <c r="O83" s="22"/>
-      <c r="P83" s="171"/>
+      <c r="P83" s="175"/>
       <c r="Q83" s="154"/>
-      <c r="R83" s="187"/>
+      <c r="R83" s="174"/>
     </row>
     <row r="84" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="171"/>
-      <c r="B84" s="171"/>
+      <c r="A84" s="175"/>
+      <c r="B84" s="175"/>
       <c r="C84" s="39" t="s">
         <v>102</v>
       </c>
@@ -7831,14 +7831,14 @@
       <c r="M84" s="22"/>
       <c r="N84" s="22"/>
       <c r="O84" s="22"/>
-      <c r="P84" s="171"/>
+      <c r="P84" s="175"/>
       <c r="Q84" s="54">
         <v>0.25</v>
       </c>
-      <c r="R84" s="187"/>
+      <c r="R84" s="174"/>
     </row>
     <row r="85" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="171"/>
+      <c r="A85" s="175"/>
       <c r="B85" s="90"/>
       <c r="C85" s="91"/>
       <c r="D85" s="92"/>
@@ -7855,16 +7855,16 @@
       <c r="O85" s="160" t="s">
         <v>103</v>
       </c>
-      <c r="P85" s="171"/>
+      <c r="P85" s="175"/>
       <c r="Q85" s="157">
         <f>(Q74+Q76+Q78+Q80+Q82+Q84)/6</f>
         <v>0.54164999999999996</v>
       </c>
-      <c r="R85" s="187"/>
+      <c r="R85" s="174"/>
     </row>
     <row r="86" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="171"/>
-      <c r="B86" s="185" t="s">
+      <c r="A86" s="175"/>
+      <c r="B86" s="184" t="s">
         <v>104</v>
       </c>
       <c r="C86" s="104" t="s">
@@ -7890,26 +7890,26 @@
       <c r="M86" s="20"/>
       <c r="N86" s="20"/>
       <c r="O86" s="20"/>
-      <c r="P86" s="171"/>
+      <c r="P86" s="175"/>
       <c r="Q86" s="154"/>
-      <c r="R86" s="187"/>
+      <c r="R86" s="174"/>
     </row>
     <row r="87" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="171"/>
-      <c r="B87" s="171"/>
+      <c r="A87" s="175"/>
+      <c r="B87" s="175"/>
       <c r="C87" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="D87" s="170">
+      <c r="D87" s="176">
         <v>0.25</v>
       </c>
-      <c r="E87" s="172">
+      <c r="E87" s="170">
         <v>0.5</v>
       </c>
-      <c r="F87" s="170">
+      <c r="F87" s="176">
         <v>1</v>
       </c>
-      <c r="G87" s="170">
+      <c r="G87" s="176">
         <v>0.75</v>
       </c>
       <c r="H87" s="20"/>
@@ -7920,18 +7920,18 @@
       <c r="M87" s="20"/>
       <c r="N87" s="20"/>
       <c r="O87" s="20"/>
-      <c r="P87" s="171"/>
-      <c r="Q87" s="166">
+      <c r="P87" s="175"/>
+      <c r="Q87" s="172">
         <v>0.5</v>
       </c>
-      <c r="R87" s="187"/>
+      <c r="R87" s="174"/>
     </row>
     <row r="88" spans="1:18" ht="180" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="171"/>
-      <c r="B88" s="171"/>
+      <c r="A88" s="175"/>
+      <c r="B88" s="175"/>
       <c r="C88" s="34"/>
       <c r="D88" s="169"/>
-      <c r="E88" s="167"/>
+      <c r="E88" s="171"/>
       <c r="F88" s="169"/>
       <c r="G88" s="169"/>
       <c r="H88" s="19"/>
@@ -7942,13 +7942,13 @@
       <c r="M88" s="19"/>
       <c r="N88" s="19"/>
       <c r="O88" s="19"/>
-      <c r="P88" s="171"/>
-      <c r="Q88" s="167"/>
-      <c r="R88" s="187"/>
+      <c r="P88" s="175"/>
+      <c r="Q88" s="171"/>
+      <c r="R88" s="174"/>
     </row>
     <row r="89" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="171"/>
-      <c r="B89" s="171"/>
+      <c r="A89" s="175"/>
+      <c r="B89" s="175"/>
       <c r="C89" s="96" t="s">
         <v>111</v>
       </c>
@@ -7970,20 +7970,20 @@
       <c r="M89" s="19"/>
       <c r="N89" s="19"/>
       <c r="O89" s="19"/>
-      <c r="P89" s="171"/>
+      <c r="P89" s="175"/>
       <c r="Q89" s="127"/>
-      <c r="R89" s="187"/>
+      <c r="R89" s="174"/>
     </row>
     <row r="90" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="171"/>
-      <c r="B90" s="171"/>
+      <c r="A90" s="175"/>
+      <c r="B90" s="175"/>
       <c r="C90" s="36" t="s">
         <v>115</v>
       </c>
       <c r="D90" s="168">
         <v>0.33329999999999999</v>
       </c>
-      <c r="E90" s="166">
+      <c r="E90" s="172">
         <v>0.66659999999999997</v>
       </c>
       <c r="F90" s="168">
@@ -7998,18 +7998,18 @@
       <c r="M90" s="19"/>
       <c r="N90" s="19"/>
       <c r="O90" s="19"/>
-      <c r="P90" s="171"/>
-      <c r="Q90" s="172">
+      <c r="P90" s="175"/>
+      <c r="Q90" s="170">
         <v>0.33329999999999999</v>
       </c>
-      <c r="R90" s="187"/>
+      <c r="R90" s="174"/>
     </row>
     <row r="91" spans="1:18" ht="153.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="171"/>
-      <c r="B91" s="171"/>
+      <c r="A91" s="175"/>
+      <c r="B91" s="175"/>
       <c r="C91" s="13"/>
       <c r="D91" s="169"/>
-      <c r="E91" s="167"/>
+      <c r="E91" s="171"/>
       <c r="F91" s="169"/>
       <c r="G91" s="24"/>
       <c r="H91" s="19"/>
@@ -8020,13 +8020,13 @@
       <c r="M91" s="19"/>
       <c r="N91" s="19"/>
       <c r="O91" s="19"/>
-      <c r="P91" s="171"/>
-      <c r="Q91" s="167"/>
-      <c r="R91" s="187"/>
+      <c r="P91" s="175"/>
+      <c r="Q91" s="171"/>
+      <c r="R91" s="174"/>
     </row>
     <row r="92" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="171"/>
-      <c r="B92" s="171"/>
+      <c r="A92" s="175"/>
+      <c r="B92" s="175"/>
       <c r="C92" s="105" t="s">
         <v>116</v>
       </c>
@@ -8048,13 +8048,13 @@
       <c r="M92" s="19"/>
       <c r="N92" s="19"/>
       <c r="O92" s="19"/>
-      <c r="P92" s="171"/>
+      <c r="P92" s="175"/>
       <c r="Q92" s="127"/>
-      <c r="R92" s="187"/>
+      <c r="R92" s="174"/>
     </row>
     <row r="93" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="171"/>
-      <c r="B93" s="171"/>
+      <c r="A93" s="175"/>
+      <c r="B93" s="175"/>
       <c r="C93" s="32" t="s">
         <v>119</v>
       </c>
@@ -8076,15 +8076,15 @@
       <c r="M93" s="19"/>
       <c r="N93" s="19"/>
       <c r="O93" s="19"/>
-      <c r="P93" s="171"/>
+      <c r="P93" s="175"/>
       <c r="Q93" s="53">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R93" s="187"/>
+      <c r="R93" s="174"/>
     </row>
     <row r="94" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="171"/>
-      <c r="B94" s="171"/>
+      <c r="A94" s="175"/>
+      <c r="B94" s="175"/>
       <c r="C94" s="96" t="s">
         <v>120</v>
       </c>
@@ -8106,13 +8106,13 @@
       <c r="M94" s="19"/>
       <c r="N94" s="19"/>
       <c r="O94" s="19"/>
-      <c r="P94" s="171"/>
+      <c r="P94" s="175"/>
       <c r="Q94" s="127"/>
-      <c r="R94" s="187"/>
+      <c r="R94" s="174"/>
     </row>
     <row r="95" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="171"/>
-      <c r="B95" s="171"/>
+      <c r="A95" s="175"/>
+      <c r="B95" s="175"/>
       <c r="C95" s="36" t="s">
         <v>124</v>
       </c>
@@ -8134,15 +8134,15 @@
       <c r="M95" s="19"/>
       <c r="N95" s="19"/>
       <c r="O95" s="19"/>
-      <c r="P95" s="171"/>
+      <c r="P95" s="175"/>
       <c r="Q95" s="53">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R95" s="187"/>
+      <c r="R95" s="174"/>
     </row>
     <row r="96" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="171"/>
-      <c r="B96" s="171"/>
+      <c r="A96" s="175"/>
+      <c r="B96" s="175"/>
       <c r="C96" s="98" t="s">
         <v>125</v>
       </c>
@@ -8166,12 +8166,12 @@
       <c r="M96" s="22"/>
       <c r="N96" s="22"/>
       <c r="O96" s="22"/>
-      <c r="P96" s="171"/>
+      <c r="P96" s="175"/>
       <c r="Q96" s="154"/>
-      <c r="R96" s="187"/>
+      <c r="R96" s="174"/>
     </row>
     <row r="97" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="171"/>
+      <c r="A97" s="175"/>
       <c r="B97" s="169"/>
       <c r="C97" s="31" t="s">
         <v>129</v>
@@ -8196,14 +8196,14 @@
       <c r="M97" s="22"/>
       <c r="N97" s="22"/>
       <c r="O97" s="22"/>
-      <c r="P97" s="171"/>
+      <c r="P97" s="175"/>
       <c r="Q97" s="53">
         <v>0.75</v>
       </c>
-      <c r="R97" s="187"/>
+      <c r="R97" s="174"/>
     </row>
     <row r="98" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="171"/>
+      <c r="A98" s="175"/>
       <c r="B98" s="73"/>
       <c r="C98" s="82"/>
       <c r="D98" s="83"/>
@@ -8220,16 +8220,16 @@
       <c r="O98" s="160" t="s">
         <v>130</v>
       </c>
-      <c r="P98" s="171"/>
+      <c r="P98" s="175"/>
       <c r="Q98" s="157">
         <f>(Q87+Q90+Q93+Q95+Q97)/5</f>
         <v>0.58329999999999993</v>
       </c>
-      <c r="R98" s="187"/>
+      <c r="R98" s="174"/>
     </row>
     <row r="99" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="171"/>
-      <c r="B99" s="185" t="s">
+      <c r="A99" s="175"/>
+      <c r="B99" s="184" t="s">
         <v>131</v>
       </c>
       <c r="C99" s="106" t="s">
@@ -8253,20 +8253,20 @@
       <c r="M99" s="20"/>
       <c r="N99" s="20"/>
       <c r="O99" s="20"/>
-      <c r="P99" s="171"/>
+      <c r="P99" s="175"/>
       <c r="Q99" s="154"/>
-      <c r="R99" s="187"/>
+      <c r="R99" s="174"/>
     </row>
     <row r="100" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="171"/>
-      <c r="B100" s="171"/>
+      <c r="A100" s="175"/>
+      <c r="B100" s="175"/>
       <c r="C100" s="64" t="s">
         <v>136</v>
       </c>
       <c r="D100" s="168">
         <v>0.66659999999999997</v>
       </c>
-      <c r="E100" s="166">
+      <c r="E100" s="172">
         <v>0.33329999999999999</v>
       </c>
       <c r="F100" s="168">
@@ -8281,18 +8281,18 @@
       <c r="M100" s="20"/>
       <c r="N100" s="20"/>
       <c r="O100" s="20"/>
-      <c r="P100" s="171"/>
-      <c r="Q100" s="166">
+      <c r="P100" s="175"/>
+      <c r="Q100" s="172">
         <v>0.33329999999999999</v>
       </c>
-      <c r="R100" s="187"/>
+      <c r="R100" s="174"/>
     </row>
     <row r="101" spans="1:18" ht="216" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="171"/>
-      <c r="B101" s="171"/>
+      <c r="A101" s="175"/>
+      <c r="B101" s="175"/>
       <c r="C101" s="65"/>
       <c r="D101" s="169"/>
-      <c r="E101" s="167"/>
+      <c r="E101" s="171"/>
       <c r="F101" s="169"/>
       <c r="G101" s="25"/>
       <c r="H101" s="18"/>
@@ -8303,13 +8303,13 @@
       <c r="M101" s="18"/>
       <c r="N101" s="18"/>
       <c r="O101" s="18"/>
-      <c r="P101" s="171"/>
-      <c r="Q101" s="167"/>
-      <c r="R101" s="187"/>
+      <c r="P101" s="175"/>
+      <c r="Q101" s="171"/>
+      <c r="R101" s="174"/>
     </row>
     <row r="102" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="171"/>
-      <c r="B102" s="171"/>
+      <c r="A102" s="175"/>
+      <c r="B102" s="175"/>
       <c r="C102" s="107" t="s">
         <v>137</v>
       </c>
@@ -8331,13 +8331,13 @@
       <c r="M102" s="18"/>
       <c r="N102" s="18"/>
       <c r="O102" s="18"/>
-      <c r="P102" s="171"/>
+      <c r="P102" s="175"/>
       <c r="Q102" s="153"/>
-      <c r="R102" s="187"/>
+      <c r="R102" s="174"/>
     </row>
     <row r="103" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="171"/>
-      <c r="B103" s="171"/>
+      <c r="A103" s="175"/>
+      <c r="B103" s="175"/>
       <c r="C103" s="64" t="s">
         <v>141</v>
       </c>
@@ -8359,15 +8359,15 @@
       <c r="M103" s="18"/>
       <c r="N103" s="18"/>
       <c r="O103" s="18"/>
-      <c r="P103" s="171"/>
+      <c r="P103" s="175"/>
       <c r="Q103" s="168">
         <v>0.33329999999999999</v>
       </c>
-      <c r="R103" s="187"/>
+      <c r="R103" s="174"/>
     </row>
     <row r="104" spans="1:18" ht="303" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="171"/>
-      <c r="B104" s="171"/>
+      <c r="A104" s="175"/>
+      <c r="B104" s="175"/>
       <c r="C104" s="64"/>
       <c r="D104" s="169"/>
       <c r="E104" s="169"/>
@@ -8381,13 +8381,13 @@
       <c r="M104" s="18"/>
       <c r="N104" s="18"/>
       <c r="O104" s="18"/>
-      <c r="P104" s="171"/>
+      <c r="P104" s="175"/>
       <c r="Q104" s="169"/>
-      <c r="R104" s="187"/>
+      <c r="R104" s="174"/>
     </row>
     <row r="105" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="171"/>
-      <c r="B105" s="171"/>
+      <c r="A105" s="175"/>
+      <c r="B105" s="175"/>
       <c r="C105" s="107" t="s">
         <v>142</v>
       </c>
@@ -8409,13 +8409,13 @@
       <c r="M105" s="18"/>
       <c r="N105" s="18"/>
       <c r="O105" s="18"/>
-      <c r="P105" s="171"/>
+      <c r="P105" s="175"/>
       <c r="Q105" s="154"/>
-      <c r="R105" s="187"/>
+      <c r="R105" s="174"/>
     </row>
     <row r="106" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="171"/>
-      <c r="B106" s="171"/>
+      <c r="A106" s="175"/>
+      <c r="B106" s="175"/>
       <c r="C106" s="64" t="s">
         <v>143</v>
       </c>
@@ -8437,15 +8437,15 @@
       <c r="M106" s="18"/>
       <c r="N106" s="18"/>
       <c r="O106" s="18"/>
-      <c r="P106" s="171"/>
+      <c r="P106" s="175"/>
       <c r="Q106" s="168">
         <v>1</v>
       </c>
-      <c r="R106" s="187"/>
+      <c r="R106" s="174"/>
     </row>
     <row r="107" spans="1:18" ht="306.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="171"/>
-      <c r="B107" s="171"/>
+      <c r="A107" s="175"/>
+      <c r="B107" s="175"/>
       <c r="C107" s="64"/>
       <c r="D107" s="169"/>
       <c r="E107" s="169"/>
@@ -8459,13 +8459,13 @@
       <c r="M107" s="18"/>
       <c r="N107" s="18"/>
       <c r="O107" s="18"/>
-      <c r="P107" s="171"/>
+      <c r="P107" s="175"/>
       <c r="Q107" s="169"/>
-      <c r="R107" s="187"/>
+      <c r="R107" s="174"/>
     </row>
     <row r="108" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="171"/>
-      <c r="B108" s="171"/>
+      <c r="A108" s="175"/>
+      <c r="B108" s="175"/>
       <c r="C108" s="107" t="s">
         <v>142</v>
       </c>
@@ -8487,13 +8487,13 @@
       <c r="M108" s="18"/>
       <c r="N108" s="18"/>
       <c r="O108" s="18"/>
-      <c r="P108" s="171"/>
+      <c r="P108" s="175"/>
       <c r="Q108" s="154"/>
-      <c r="R108" s="187"/>
+      <c r="R108" s="174"/>
     </row>
     <row r="109" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="171"/>
-      <c r="B109" s="171"/>
+      <c r="A109" s="175"/>
+      <c r="B109" s="175"/>
       <c r="C109" s="63" t="s">
         <v>144</v>
       </c>
@@ -8515,11 +8515,11 @@
       <c r="M109" s="18"/>
       <c r="N109" s="18"/>
       <c r="O109" s="18"/>
-      <c r="P109" s="171"/>
+      <c r="P109" s="175"/>
       <c r="Q109" s="168">
         <v>0.33329999999999999</v>
       </c>
-      <c r="R109" s="187"/>
+      <c r="R109" s="174"/>
     </row>
     <row r="110" spans="1:18" ht="305.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="68"/>
@@ -8537,9 +8537,9 @@
       <c r="M110" s="18"/>
       <c r="N110" s="18"/>
       <c r="O110" s="18"/>
-      <c r="P110" s="171"/>
+      <c r="P110" s="175"/>
       <c r="Q110" s="169"/>
-      <c r="R110" s="187"/>
+      <c r="R110" s="174"/>
     </row>
     <row r="111" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="69"/>
@@ -8559,18 +8559,18 @@
       <c r="O111" s="161" t="s">
         <v>145</v>
       </c>
-      <c r="P111" s="171"/>
+      <c r="P111" s="175"/>
       <c r="Q111" s="157">
         <f>(Q100+Q106+Q109)/2</f>
         <v>0.83329999999999993</v>
       </c>
-      <c r="R111" s="187"/>
+      <c r="R111" s="174"/>
     </row>
     <row r="112" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="182" t="s">
+      <c r="A112" s="198" t="s">
         <v>146</v>
       </c>
-      <c r="B112" s="185" t="s">
+      <c r="B112" s="184" t="s">
         <v>147</v>
       </c>
       <c r="C112" s="97" t="s">
@@ -8596,26 +8596,26 @@
       <c r="M112" s="20"/>
       <c r="N112" s="20"/>
       <c r="O112" s="20"/>
-      <c r="P112" s="171"/>
+      <c r="P112" s="175"/>
       <c r="Q112" s="156"/>
-      <c r="R112" s="187"/>
+      <c r="R112" s="174"/>
     </row>
     <row r="113" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="181"/>
-      <c r="B113" s="171"/>
+      <c r="B113" s="175"/>
       <c r="C113" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="D113" s="170">
+      <c r="D113" s="176">
         <v>1</v>
       </c>
-      <c r="E113" s="176">
+      <c r="E113" s="192">
         <v>0.75</v>
       </c>
-      <c r="F113" s="177">
+      <c r="F113" s="189">
         <v>0.25</v>
       </c>
-      <c r="G113" s="177">
+      <c r="G113" s="189">
         <v>0.5</v>
       </c>
       <c r="H113" s="20"/>
@@ -8626,18 +8626,18 @@
       <c r="M113" s="20"/>
       <c r="N113" s="20"/>
       <c r="O113" s="20"/>
-      <c r="P113" s="171"/>
-      <c r="Q113" s="172">
+      <c r="P113" s="175"/>
+      <c r="Q113" s="170">
         <v>0.75</v>
       </c>
-      <c r="R113" s="187"/>
+      <c r="R113" s="174"/>
     </row>
     <row r="114" spans="1:18" ht="206.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="181"/>
-      <c r="B114" s="171"/>
+      <c r="B114" s="175"/>
       <c r="C114" s="12"/>
       <c r="D114" s="169"/>
-      <c r="E114" s="167"/>
+      <c r="E114" s="171"/>
       <c r="F114" s="169"/>
       <c r="G114" s="169"/>
       <c r="H114" s="26"/>
@@ -8648,13 +8648,13 @@
       <c r="M114" s="26"/>
       <c r="N114" s="26"/>
       <c r="O114" s="26"/>
-      <c r="P114" s="171"/>
-      <c r="Q114" s="167"/>
-      <c r="R114" s="187"/>
+      <c r="P114" s="175"/>
+      <c r="Q114" s="171"/>
+      <c r="R114" s="174"/>
     </row>
     <row r="115" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="181"/>
-      <c r="B115" s="171"/>
+      <c r="B115" s="175"/>
       <c r="C115" s="96" t="s">
         <v>154</v>
       </c>
@@ -8678,26 +8678,26 @@
       <c r="M115" s="20"/>
       <c r="N115" s="20"/>
       <c r="O115" s="20"/>
-      <c r="P115" s="171"/>
+      <c r="P115" s="175"/>
       <c r="Q115" s="151"/>
-      <c r="R115" s="187"/>
+      <c r="R115" s="174"/>
     </row>
     <row r="116" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="181"/>
-      <c r="B116" s="171"/>
+      <c r="B116" s="175"/>
       <c r="C116" s="36" t="s">
         <v>155</v>
       </c>
       <c r="D116" s="168">
         <v>1</v>
       </c>
-      <c r="E116" s="198">
+      <c r="E116" s="180">
         <v>0.25</v>
       </c>
-      <c r="F116" s="190">
+      <c r="F116" s="182">
         <v>0.5</v>
       </c>
-      <c r="G116" s="190">
+      <c r="G116" s="182">
         <v>0.75</v>
       </c>
       <c r="H116" s="20"/>
@@ -8708,18 +8708,18 @@
       <c r="M116" s="20"/>
       <c r="N116" s="20"/>
       <c r="O116" s="20"/>
-      <c r="P116" s="171"/>
-      <c r="Q116" s="172">
+      <c r="P116" s="175"/>
+      <c r="Q116" s="170">
         <v>0.5</v>
       </c>
-      <c r="R116" s="187"/>
+      <c r="R116" s="174"/>
     </row>
     <row r="117" spans="1:18" ht="205.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="181"/>
-      <c r="B117" s="171"/>
+      <c r="B117" s="175"/>
       <c r="C117" s="13"/>
       <c r="D117" s="169"/>
-      <c r="E117" s="167"/>
+      <c r="E117" s="171"/>
       <c r="F117" s="169"/>
       <c r="G117" s="169"/>
       <c r="H117" s="27"/>
@@ -8730,13 +8730,13 @@
       <c r="M117" s="27"/>
       <c r="N117" s="27"/>
       <c r="O117" s="27"/>
-      <c r="P117" s="171"/>
-      <c r="Q117" s="167"/>
-      <c r="R117" s="187"/>
+      <c r="P117" s="175"/>
+      <c r="Q117" s="171"/>
+      <c r="R117" s="174"/>
     </row>
     <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" s="181"/>
-      <c r="B118" s="171"/>
+      <c r="B118" s="175"/>
       <c r="C118" s="98" t="s">
         <v>156</v>
       </c>
@@ -8762,20 +8762,20 @@
       <c r="M118" s="22"/>
       <c r="N118" s="22"/>
       <c r="O118" s="22"/>
-      <c r="P118" s="171"/>
+      <c r="P118" s="175"/>
       <c r="Q118" s="153"/>
-      <c r="R118" s="187"/>
+      <c r="R118" s="174"/>
     </row>
     <row r="119" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="181"/>
-      <c r="B119" s="171"/>
+      <c r="B119" s="175"/>
       <c r="C119" s="40" t="s">
         <v>162</v>
       </c>
       <c r="D119" s="168">
         <v>0.2</v>
       </c>
-      <c r="E119" s="166">
+      <c r="E119" s="172">
         <v>0.4</v>
       </c>
       <c r="F119" s="168">
@@ -8794,18 +8794,18 @@
       <c r="M119" s="22"/>
       <c r="N119" s="22"/>
       <c r="O119" s="22"/>
-      <c r="P119" s="171"/>
-      <c r="Q119" s="166">
+      <c r="P119" s="175"/>
+      <c r="Q119" s="172">
         <v>1</v>
       </c>
-      <c r="R119" s="187"/>
+      <c r="R119" s="174"/>
     </row>
     <row r="120" spans="1:18" ht="245.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="181"/>
-      <c r="B120" s="171"/>
+      <c r="B120" s="175"/>
       <c r="C120" s="34"/>
       <c r="D120" s="169"/>
-      <c r="E120" s="167"/>
+      <c r="E120" s="171"/>
       <c r="F120" s="169"/>
       <c r="G120" s="169"/>
       <c r="H120" s="169"/>
@@ -8816,13 +8816,13 @@
       <c r="M120" s="22"/>
       <c r="N120" s="22"/>
       <c r="O120" s="22"/>
-      <c r="P120" s="171"/>
-      <c r="Q120" s="167"/>
-      <c r="R120" s="187"/>
+      <c r="P120" s="175"/>
+      <c r="Q120" s="171"/>
+      <c r="R120" s="174"/>
     </row>
     <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" s="181"/>
-      <c r="B121" s="171"/>
+      <c r="B121" s="175"/>
       <c r="C121" s="98" t="s">
         <v>163</v>
       </c>
@@ -8844,13 +8844,13 @@
       <c r="M121" s="22"/>
       <c r="N121" s="22"/>
       <c r="O121" s="22"/>
-      <c r="P121" s="171"/>
+      <c r="P121" s="175"/>
       <c r="Q121" s="139"/>
-      <c r="R121" s="187"/>
+      <c r="R121" s="174"/>
     </row>
     <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" s="181"/>
-      <c r="B122" s="171"/>
+      <c r="B122" s="175"/>
       <c r="C122" s="64" t="s">
         <v>167</v>
       </c>
@@ -8872,15 +8872,15 @@
       <c r="M122" s="22"/>
       <c r="N122" s="22"/>
       <c r="O122" s="22"/>
-      <c r="P122" s="171"/>
+      <c r="P122" s="175"/>
       <c r="Q122" s="168">
         <v>1</v>
       </c>
-      <c r="R122" s="187"/>
+      <c r="R122" s="174"/>
     </row>
     <row r="123" spans="1:18" ht="336.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="181"/>
-      <c r="B123" s="171"/>
+      <c r="B123" s="175"/>
       <c r="C123" s="34"/>
       <c r="D123" s="169"/>
       <c r="E123" s="169"/>
@@ -8894,13 +8894,13 @@
       <c r="M123" s="22"/>
       <c r="N123" s="22"/>
       <c r="O123" s="22"/>
-      <c r="P123" s="171"/>
+      <c r="P123" s="175"/>
       <c r="Q123" s="169"/>
-      <c r="R123" s="187"/>
+      <c r="R123" s="174"/>
     </row>
     <row r="124" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="181"/>
-      <c r="B124" s="171"/>
+      <c r="B124" s="175"/>
       <c r="C124" s="96" t="s">
         <v>168</v>
       </c>
@@ -8928,13 +8928,13 @@
       <c r="M124" s="22"/>
       <c r="N124" s="22"/>
       <c r="O124" s="22"/>
-      <c r="P124" s="171"/>
+      <c r="P124" s="175"/>
       <c r="Q124" s="153"/>
-      <c r="R124" s="187"/>
+      <c r="R124" s="174"/>
     </row>
     <row r="125" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="181"/>
-      <c r="B125" s="171"/>
+      <c r="B125" s="175"/>
       <c r="C125" s="36" t="s">
         <v>175</v>
       </c>
@@ -8962,15 +8962,15 @@
       <c r="M125" s="22"/>
       <c r="N125" s="22"/>
       <c r="O125" s="22"/>
-      <c r="P125" s="171"/>
+      <c r="P125" s="175"/>
       <c r="Q125" s="51">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R125" s="187"/>
+      <c r="R125" s="174"/>
     </row>
     <row r="126" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="181"/>
-      <c r="B126" s="171"/>
+      <c r="B126" s="175"/>
       <c r="C126" s="96" t="s">
         <v>176</v>
       </c>
@@ -8992,13 +8992,13 @@
       <c r="M126" s="22"/>
       <c r="N126" s="22"/>
       <c r="O126" s="22"/>
-      <c r="P126" s="171"/>
+      <c r="P126" s="175"/>
       <c r="Q126" s="153"/>
-      <c r="R126" s="187"/>
+      <c r="R126" s="174"/>
     </row>
     <row r="127" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="181"/>
-      <c r="B127" s="171"/>
+      <c r="B127" s="175"/>
       <c r="C127" s="32" t="s">
         <v>180</v>
       </c>
@@ -9020,15 +9020,15 @@
       <c r="M127" s="22"/>
       <c r="N127" s="22"/>
       <c r="O127" s="22"/>
-      <c r="P127" s="171"/>
+      <c r="P127" s="175"/>
       <c r="Q127" s="52">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R127" s="187"/>
+      <c r="R127" s="174"/>
     </row>
     <row r="128" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="181"/>
-      <c r="B128" s="171"/>
+      <c r="B128" s="175"/>
       <c r="C128" s="105" t="s">
         <v>181</v>
       </c>
@@ -9050,13 +9050,13 @@
       <c r="M128" s="22"/>
       <c r="N128" s="22"/>
       <c r="O128" s="22"/>
-      <c r="P128" s="171"/>
+      <c r="P128" s="175"/>
       <c r="Q128" s="153"/>
-      <c r="R128" s="187"/>
+      <c r="R128" s="174"/>
     </row>
     <row r="129" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="181"/>
-      <c r="B129" s="171"/>
+      <c r="B129" s="175"/>
       <c r="C129" s="32" t="s">
         <v>185</v>
       </c>
@@ -9078,15 +9078,15 @@
       <c r="M129" s="22"/>
       <c r="N129" s="22"/>
       <c r="O129" s="22"/>
-      <c r="P129" s="171"/>
+      <c r="P129" s="175"/>
       <c r="Q129" s="52">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R129" s="187"/>
+      <c r="R129" s="174"/>
     </row>
     <row r="130" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="181"/>
-      <c r="B130" s="171"/>
+      <c r="B130" s="175"/>
       <c r="C130" s="105" t="s">
         <v>186</v>
       </c>
@@ -9108,13 +9108,13 @@
       <c r="M130" s="22"/>
       <c r="N130" s="22"/>
       <c r="O130" s="22"/>
-      <c r="P130" s="171"/>
+      <c r="P130" s="175"/>
       <c r="Q130" s="153"/>
-      <c r="R130" s="187"/>
+      <c r="R130" s="174"/>
     </row>
     <row r="131" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="181"/>
-      <c r="B131" s="171"/>
+      <c r="B131" s="175"/>
       <c r="C131" s="32" t="s">
         <v>190</v>
       </c>
@@ -9136,15 +9136,15 @@
       <c r="M131" s="22"/>
       <c r="N131" s="22"/>
       <c r="O131" s="22"/>
-      <c r="P131" s="171"/>
+      <c r="P131" s="175"/>
       <c r="Q131" s="52">
         <v>0.33329999999999999</v>
       </c>
-      <c r="R131" s="187"/>
+      <c r="R131" s="174"/>
     </row>
     <row r="132" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="181"/>
-      <c r="B132" s="171"/>
+      <c r="B132" s="175"/>
       <c r="C132" s="105" t="s">
         <v>191</v>
       </c>
@@ -9166,13 +9166,13 @@
       <c r="M132" s="22"/>
       <c r="N132" s="22"/>
       <c r="O132" s="22"/>
-      <c r="P132" s="171"/>
+      <c r="P132" s="175"/>
       <c r="Q132" s="153"/>
-      <c r="R132" s="187"/>
+      <c r="R132" s="174"/>
     </row>
     <row r="133" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="181"/>
-      <c r="B133" s="171"/>
+      <c r="B133" s="175"/>
       <c r="C133" s="32" t="s">
         <v>195</v>
       </c>
@@ -9194,15 +9194,15 @@
       <c r="M133" s="22"/>
       <c r="N133" s="22"/>
       <c r="O133" s="22"/>
-      <c r="P133" s="171"/>
+      <c r="P133" s="175"/>
       <c r="Q133" s="52">
         <v>0.33329999999999999</v>
       </c>
-      <c r="R133" s="187"/>
+      <c r="R133" s="174"/>
     </row>
     <row r="134" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="181"/>
-      <c r="B134" s="171"/>
+      <c r="B134" s="175"/>
       <c r="C134" s="105" t="s">
         <v>196</v>
       </c>
@@ -9224,13 +9224,13 @@
       <c r="M134" s="22"/>
       <c r="N134" s="22"/>
       <c r="O134" s="22"/>
-      <c r="P134" s="171"/>
+      <c r="P134" s="175"/>
       <c r="Q134" s="153"/>
-      <c r="R134" s="187"/>
+      <c r="R134" s="174"/>
     </row>
     <row r="135" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="181"/>
-      <c r="B135" s="171"/>
+      <c r="B135" s="175"/>
       <c r="C135" s="32" t="s">
         <v>200</v>
       </c>
@@ -9252,15 +9252,15 @@
       <c r="M135" s="22"/>
       <c r="N135" s="22"/>
       <c r="O135" s="22"/>
-      <c r="P135" s="171"/>
+      <c r="P135" s="175"/>
       <c r="Q135" s="52">
         <v>1</v>
       </c>
-      <c r="R135" s="187"/>
+      <c r="R135" s="174"/>
     </row>
     <row r="136" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="181"/>
-      <c r="B136" s="171"/>
+      <c r="B136" s="175"/>
       <c r="C136" s="96" t="s">
         <v>201</v>
       </c>
@@ -9282,9 +9282,9 @@
       <c r="M136" s="22"/>
       <c r="N136" s="22"/>
       <c r="O136" s="22"/>
-      <c r="P136" s="171"/>
+      <c r="P136" s="175"/>
       <c r="Q136" s="153"/>
-      <c r="R136" s="187"/>
+      <c r="R136" s="174"/>
     </row>
     <row r="137" spans="1:18" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="181"/>
@@ -9310,11 +9310,11 @@
       <c r="M137" s="22"/>
       <c r="N137" s="22"/>
       <c r="O137" s="22"/>
-      <c r="P137" s="171"/>
+      <c r="P137" s="175"/>
       <c r="Q137" s="51">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R137" s="187"/>
+      <c r="R137" s="174"/>
     </row>
     <row r="138" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="70"/>
@@ -9334,18 +9334,18 @@
       <c r="O138" s="160" t="s">
         <v>206</v>
       </c>
-      <c r="P138" s="171"/>
+      <c r="P138" s="175"/>
       <c r="Q138" s="157">
         <f>(Q113+Q116+Q119+Q122+Q125+Q127+Q129+Q131+Q133+Q135+Q137)/11</f>
         <v>0.6893636363636364</v>
       </c>
-      <c r="R138" s="187"/>
+      <c r="R138" s="174"/>
     </row>
     <row r="139" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="180" t="s">
+      <c r="A139" s="197" t="s">
         <v>207</v>
       </c>
-      <c r="B139" s="186" t="s">
+      <c r="B139" s="185" t="s">
         <v>208</v>
       </c>
       <c r="C139" s="97" t="s">
@@ -9371,20 +9371,20 @@
       <c r="M139" s="20"/>
       <c r="N139" s="20"/>
       <c r="O139" s="20"/>
-      <c r="P139" s="171"/>
+      <c r="P139" s="175"/>
       <c r="Q139" s="156"/>
-      <c r="R139" s="187"/>
+      <c r="R139" s="174"/>
     </row>
     <row r="140" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="181"/>
-      <c r="B140" s="187"/>
+      <c r="B140" s="174"/>
       <c r="C140" s="36" t="s">
         <v>214</v>
       </c>
       <c r="D140" s="168">
         <v>1</v>
       </c>
-      <c r="E140" s="166">
+      <c r="E140" s="172">
         <v>0.75</v>
       </c>
       <c r="F140" s="168">
@@ -9401,18 +9401,18 @@
       <c r="M140" s="20"/>
       <c r="N140" s="20"/>
       <c r="O140" s="20"/>
-      <c r="P140" s="171"/>
-      <c r="Q140" s="172">
+      <c r="P140" s="175"/>
+      <c r="Q140" s="170">
         <v>0.75</v>
       </c>
-      <c r="R140" s="187"/>
+      <c r="R140" s="174"/>
     </row>
     <row r="141" spans="1:18" ht="199.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="181"/>
-      <c r="B141" s="187"/>
+      <c r="B141" s="174"/>
       <c r="C141" s="12"/>
       <c r="D141" s="169"/>
-      <c r="E141" s="167"/>
+      <c r="E141" s="171"/>
       <c r="F141" s="169"/>
       <c r="G141" s="169"/>
       <c r="H141" s="18"/>
@@ -9423,13 +9423,13 @@
       <c r="M141" s="18"/>
       <c r="N141" s="18"/>
       <c r="O141" s="18"/>
-      <c r="P141" s="171"/>
-      <c r="Q141" s="167"/>
-      <c r="R141" s="187"/>
+      <c r="P141" s="175"/>
+      <c r="Q141" s="171"/>
+      <c r="R141" s="174"/>
     </row>
     <row r="142" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="181"/>
-      <c r="B142" s="187"/>
+      <c r="B142" s="174"/>
       <c r="C142" s="96" t="s">
         <v>215</v>
       </c>
@@ -9453,26 +9453,26 @@
       <c r="M142" s="20"/>
       <c r="N142" s="20"/>
       <c r="O142" s="20"/>
-      <c r="P142" s="171"/>
+      <c r="P142" s="175"/>
       <c r="Q142" s="151"/>
-      <c r="R142" s="187"/>
+      <c r="R142" s="174"/>
     </row>
     <row r="143" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="181"/>
-      <c r="B143" s="187"/>
+      <c r="B143" s="174"/>
       <c r="C143" s="36" t="s">
         <v>220</v>
       </c>
-      <c r="D143" s="170">
+      <c r="D143" s="176">
         <v>0.25</v>
       </c>
-      <c r="E143" s="172">
+      <c r="E143" s="170">
         <v>0.5</v>
       </c>
-      <c r="F143" s="170">
+      <c r="F143" s="176">
         <v>0.75</v>
       </c>
-      <c r="G143" s="170">
+      <c r="G143" s="176">
         <v>1</v>
       </c>
       <c r="H143" s="20"/>
@@ -9483,18 +9483,18 @@
       <c r="M143" s="20"/>
       <c r="N143" s="20"/>
       <c r="O143" s="20"/>
-      <c r="P143" s="171"/>
-      <c r="Q143" s="172">
+      <c r="P143" s="175"/>
+      <c r="Q143" s="170">
         <v>0.25</v>
       </c>
-      <c r="R143" s="187"/>
+      <c r="R143" s="174"/>
     </row>
     <row r="144" spans="1:18" ht="199.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="181"/>
-      <c r="B144" s="187"/>
+      <c r="B144" s="174"/>
       <c r="C144" s="12"/>
       <c r="D144" s="169"/>
-      <c r="E144" s="167"/>
+      <c r="E144" s="171"/>
       <c r="F144" s="169"/>
       <c r="G144" s="169"/>
       <c r="H144" s="19"/>
@@ -9505,13 +9505,13 @@
       <c r="M144" s="19"/>
       <c r="N144" s="19"/>
       <c r="O144" s="19"/>
-      <c r="P144" s="171"/>
-      <c r="Q144" s="167"/>
-      <c r="R144" s="187"/>
+      <c r="P144" s="175"/>
+      <c r="Q144" s="171"/>
+      <c r="R144" s="174"/>
     </row>
     <row r="145" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="181"/>
-      <c r="B145" s="187"/>
+      <c r="B145" s="174"/>
       <c r="C145" s="96" t="s">
         <v>221</v>
       </c>
@@ -9531,13 +9531,13 @@
       <c r="M145" s="18"/>
       <c r="N145" s="18"/>
       <c r="O145" s="18"/>
-      <c r="P145" s="171"/>
+      <c r="P145" s="175"/>
       <c r="Q145" s="151"/>
-      <c r="R145" s="187"/>
+      <c r="R145" s="174"/>
     </row>
     <row r="146" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="181"/>
-      <c r="B146" s="187"/>
+      <c r="B146" s="174"/>
       <c r="C146" s="32" t="s">
         <v>224</v>
       </c>
@@ -9557,15 +9557,15 @@
       <c r="M146" s="18"/>
       <c r="N146" s="18"/>
       <c r="O146" s="18"/>
-      <c r="P146" s="171"/>
+      <c r="P146" s="175"/>
       <c r="Q146" s="52">
         <v>0.75</v>
       </c>
-      <c r="R146" s="187"/>
+      <c r="R146" s="174"/>
     </row>
     <row r="147" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="181"/>
-      <c r="B147" s="187"/>
+      <c r="B147" s="174"/>
       <c r="C147" s="96" t="s">
         <v>225</v>
       </c>
@@ -9585,13 +9585,13 @@
       <c r="M147" s="18"/>
       <c r="N147" s="18"/>
       <c r="O147" s="18"/>
-      <c r="P147" s="171"/>
+      <c r="P147" s="175"/>
       <c r="Q147" s="153"/>
-      <c r="R147" s="187"/>
+      <c r="R147" s="174"/>
     </row>
     <row r="148" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="181"/>
-      <c r="B148" s="187"/>
+      <c r="B148" s="174"/>
       <c r="C148" s="32" t="s">
         <v>228</v>
       </c>
@@ -9611,15 +9611,15 @@
       <c r="M148" s="18"/>
       <c r="N148" s="18"/>
       <c r="O148" s="18"/>
-      <c r="P148" s="171"/>
+      <c r="P148" s="175"/>
       <c r="Q148" s="52">
         <v>0.75</v>
       </c>
-      <c r="R148" s="187"/>
+      <c r="R148" s="174"/>
     </row>
     <row r="149" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="181"/>
-      <c r="B149" s="187"/>
+      <c r="B149" s="174"/>
       <c r="C149" s="105" t="s">
         <v>229</v>
       </c>
@@ -9639,13 +9639,13 @@
       <c r="M149" s="18"/>
       <c r="N149" s="18"/>
       <c r="O149" s="18"/>
-      <c r="P149" s="171"/>
+      <c r="P149" s="175"/>
       <c r="Q149" s="153"/>
-      <c r="R149" s="187"/>
+      <c r="R149" s="174"/>
     </row>
     <row r="150" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="181"/>
-      <c r="B150" s="187"/>
+      <c r="B150" s="174"/>
       <c r="C150" s="32" t="s">
         <v>232</v>
       </c>
@@ -9665,15 +9665,15 @@
       <c r="M150" s="18"/>
       <c r="N150" s="18"/>
       <c r="O150" s="18"/>
-      <c r="P150" s="171"/>
+      <c r="P150" s="175"/>
       <c r="Q150" s="52">
         <v>0.75</v>
       </c>
-      <c r="R150" s="187"/>
+      <c r="R150" s="174"/>
     </row>
     <row r="151" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="181"/>
-      <c r="B151" s="187"/>
+      <c r="B151" s="174"/>
       <c r="C151" s="108" t="s">
         <v>233</v>
       </c>
@@ -9697,13 +9697,13 @@
       <c r="M151" s="20"/>
       <c r="N151" s="20"/>
       <c r="O151" s="20"/>
-      <c r="P151" s="171"/>
+      <c r="P151" s="175"/>
       <c r="Q151" s="151"/>
-      <c r="R151" s="187"/>
+      <c r="R151" s="174"/>
     </row>
     <row r="152" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="181"/>
-      <c r="B152" s="187"/>
+      <c r="B152" s="174"/>
       <c r="C152" s="41" t="s">
         <v>238</v>
       </c>
@@ -9727,15 +9727,15 @@
       <c r="M152" s="20"/>
       <c r="N152" s="20"/>
       <c r="O152" s="20"/>
-      <c r="P152" s="171"/>
+      <c r="P152" s="175"/>
       <c r="Q152" s="62">
         <v>0.5</v>
       </c>
-      <c r="R152" s="187"/>
+      <c r="R152" s="174"/>
     </row>
     <row r="153" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="181"/>
-      <c r="B153" s="187"/>
+      <c r="B153" s="174"/>
       <c r="C153" s="96" t="s">
         <v>239</v>
       </c>
@@ -9755,13 +9755,13 @@
       <c r="M153" s="18"/>
       <c r="N153" s="18"/>
       <c r="O153" s="18"/>
-      <c r="P153" s="171"/>
+      <c r="P153" s="175"/>
       <c r="Q153" s="153"/>
-      <c r="R153" s="187"/>
+      <c r="R153" s="174"/>
     </row>
     <row r="154" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="181"/>
-      <c r="B154" s="187"/>
+      <c r="B154" s="174"/>
       <c r="C154" s="32" t="s">
         <v>242</v>
       </c>
@@ -9781,15 +9781,15 @@
       <c r="M154" s="18"/>
       <c r="N154" s="18"/>
       <c r="O154" s="18"/>
-      <c r="P154" s="171"/>
+      <c r="P154" s="175"/>
       <c r="Q154" s="52">
         <v>0.25</v>
       </c>
-      <c r="R154" s="187"/>
+      <c r="R154" s="174"/>
     </row>
     <row r="155" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="181"/>
-      <c r="B155" s="187"/>
+      <c r="B155" s="174"/>
       <c r="C155" s="96" t="s">
         <v>243</v>
       </c>
@@ -9813,13 +9813,13 @@
       <c r="M155" s="20"/>
       <c r="N155" s="20"/>
       <c r="O155" s="20"/>
-      <c r="P155" s="171"/>
+      <c r="P155" s="175"/>
       <c r="Q155" s="153"/>
-      <c r="R155" s="187"/>
+      <c r="R155" s="174"/>
     </row>
     <row r="156" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="181"/>
-      <c r="B156" s="187"/>
+      <c r="B156" s="174"/>
       <c r="C156" s="43" t="s">
         <v>248</v>
       </c>
@@ -9843,15 +9843,15 @@
       <c r="M156" s="19"/>
       <c r="N156" s="19"/>
       <c r="O156" s="19"/>
-      <c r="P156" s="171"/>
+      <c r="P156" s="175"/>
       <c r="Q156" s="52">
         <v>0.75</v>
       </c>
-      <c r="R156" s="187"/>
+      <c r="R156" s="174"/>
     </row>
     <row r="157" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="181"/>
-      <c r="B157" s="187"/>
+      <c r="B157" s="174"/>
       <c r="C157" s="96" t="s">
         <v>249</v>
       </c>
@@ -9873,13 +9873,13 @@
       <c r="M157" s="18"/>
       <c r="N157" s="18"/>
       <c r="O157" s="18"/>
-      <c r="P157" s="171"/>
+      <c r="P157" s="175"/>
       <c r="Q157" s="153"/>
-      <c r="R157" s="187"/>
+      <c r="R157" s="174"/>
     </row>
     <row r="158" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="181"/>
-      <c r="B158" s="187"/>
+      <c r="B158" s="174"/>
       <c r="C158" s="32" t="s">
         <v>253</v>
       </c>
@@ -9901,15 +9901,15 @@
       <c r="M158" s="18"/>
       <c r="N158" s="18"/>
       <c r="O158" s="18"/>
-      <c r="P158" s="171"/>
+      <c r="P158" s="175"/>
       <c r="Q158" s="52">
         <v>0.66659999999999997</v>
       </c>
-      <c r="R158" s="187"/>
+      <c r="R158" s="174"/>
     </row>
     <row r="159" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="181"/>
-      <c r="B159" s="187"/>
+      <c r="B159" s="174"/>
       <c r="C159" s="96" t="s">
         <v>254</v>
       </c>
@@ -9933,13 +9933,13 @@
       <c r="M159" s="20"/>
       <c r="N159" s="20"/>
       <c r="O159" s="20"/>
-      <c r="P159" s="171"/>
+      <c r="P159" s="175"/>
       <c r="Q159" s="151"/>
-      <c r="R159" s="187"/>
+      <c r="R159" s="174"/>
     </row>
     <row r="160" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="181"/>
-      <c r="B160" s="187"/>
+      <c r="B160" s="174"/>
       <c r="C160" s="44" t="s">
         <v>259</v>
       </c>
@@ -9963,15 +9963,15 @@
       <c r="M160" s="18"/>
       <c r="N160" s="18"/>
       <c r="O160" s="18"/>
-      <c r="P160" s="171"/>
+      <c r="P160" s="175"/>
       <c r="Q160" s="52">
         <v>0.5</v>
       </c>
-      <c r="R160" s="187"/>
+      <c r="R160" s="174"/>
     </row>
     <row r="161" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="181"/>
-      <c r="B161" s="187"/>
+      <c r="B161" s="174"/>
       <c r="C161" s="96" t="s">
         <v>260</v>
       </c>
@@ -9981,8 +9981,8 @@
       <c r="E161" s="110" t="s">
         <v>262</v>
       </c>
-      <c r="F161" s="189"/>
-      <c r="G161" s="187"/>
+      <c r="F161" s="187"/>
+      <c r="G161" s="174"/>
       <c r="H161" s="22"/>
       <c r="I161" s="22"/>
       <c r="J161" s="22"/>
@@ -9991,13 +9991,13 @@
       <c r="M161" s="22"/>
       <c r="N161" s="22"/>
       <c r="O161" s="22"/>
-      <c r="P161" s="171"/>
+      <c r="P161" s="175"/>
       <c r="Q161" s="153"/>
-      <c r="R161" s="187"/>
+      <c r="R161" s="174"/>
     </row>
     <row r="162" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="181"/>
-      <c r="B162" s="187"/>
+      <c r="B162" s="174"/>
       <c r="C162" s="45" t="s">
         <v>263</v>
       </c>
@@ -10007,8 +10007,8 @@
       <c r="E162" s="49">
         <v>0.75</v>
       </c>
-      <c r="F162" s="187"/>
-      <c r="G162" s="187"/>
+      <c r="F162" s="174"/>
+      <c r="G162" s="174"/>
       <c r="H162" s="22"/>
       <c r="I162" s="22"/>
       <c r="J162" s="22"/>
@@ -10017,20 +10017,20 @@
       <c r="M162" s="22"/>
       <c r="N162" s="22"/>
       <c r="O162" s="22"/>
-      <c r="P162" s="171"/>
+      <c r="P162" s="175"/>
       <c r="Q162" s="168"/>
-      <c r="R162" s="187"/>
+      <c r="R162" s="174"/>
     </row>
     <row r="163" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="181"/>
-      <c r="B163" s="187"/>
+      <c r="B163" s="174"/>
       <c r="C163" s="46" t="s">
         <v>264</v>
       </c>
       <c r="D163" s="60"/>
       <c r="E163" s="18"/>
-      <c r="F163" s="187"/>
-      <c r="G163" s="187"/>
+      <c r="F163" s="174"/>
+      <c r="G163" s="174"/>
       <c r="H163" s="22"/>
       <c r="I163" s="22"/>
       <c r="J163" s="22"/>
@@ -10039,20 +10039,20 @@
       <c r="M163" s="22"/>
       <c r="N163" s="22"/>
       <c r="O163" s="22"/>
-      <c r="P163" s="171"/>
-      <c r="Q163" s="171"/>
-      <c r="R163" s="187"/>
+      <c r="P163" s="175"/>
+      <c r="Q163" s="175"/>
+      <c r="R163" s="174"/>
     </row>
     <row r="164" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="181"/>
-      <c r="B164" s="187"/>
+      <c r="B164" s="174"/>
       <c r="C164" s="46" t="s">
         <v>265</v>
       </c>
       <c r="D164" s="60"/>
       <c r="E164" s="18"/>
-      <c r="F164" s="187"/>
-      <c r="G164" s="187"/>
+      <c r="F164" s="174"/>
+      <c r="G164" s="174"/>
       <c r="H164" s="22"/>
       <c r="I164" s="22"/>
       <c r="J164" s="22"/>
@@ -10061,13 +10061,13 @@
       <c r="M164" s="22"/>
       <c r="N164" s="22"/>
       <c r="O164" s="22"/>
-      <c r="P164" s="171"/>
-      <c r="Q164" s="171"/>
-      <c r="R164" s="187"/>
+      <c r="P164" s="175"/>
+      <c r="Q164" s="175"/>
+      <c r="R164" s="174"/>
     </row>
     <row r="165" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="181"/>
-      <c r="B165" s="187"/>
+      <c r="B165" s="174"/>
       <c r="C165" s="47" t="s">
         <v>266</v>
       </c>
@@ -10076,8 +10076,8 @@
         <v>0</v>
       </c>
       <c r="E165" s="18"/>
-      <c r="F165" s="187"/>
-      <c r="G165" s="187"/>
+      <c r="F165" s="174"/>
+      <c r="G165" s="174"/>
       <c r="H165" s="22"/>
       <c r="I165" s="22"/>
       <c r="J165" s="22"/>
@@ -10086,13 +10086,13 @@
       <c r="M165" s="22"/>
       <c r="N165" s="22"/>
       <c r="O165" s="22"/>
-      <c r="P165" s="171"/>
+      <c r="P165" s="175"/>
       <c r="Q165" s="169"/>
-      <c r="R165" s="187"/>
+      <c r="R165" s="174"/>
     </row>
     <row r="166" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="181"/>
-      <c r="B166" s="187"/>
+      <c r="B166" s="174"/>
       <c r="C166" s="96" t="s">
         <v>267</v>
       </c>
@@ -10102,8 +10102,8 @@
       <c r="E166" s="110" t="s">
         <v>269</v>
       </c>
-      <c r="F166" s="187"/>
-      <c r="G166" s="187"/>
+      <c r="F166" s="174"/>
+      <c r="G166" s="174"/>
       <c r="H166" s="22"/>
       <c r="I166" s="22"/>
       <c r="J166" s="22"/>
@@ -10112,13 +10112,13 @@
       <c r="M166" s="22"/>
       <c r="N166" s="22"/>
       <c r="O166" s="22"/>
-      <c r="P166" s="171"/>
+      <c r="P166" s="175"/>
       <c r="Q166" s="153"/>
-      <c r="R166" s="187"/>
+      <c r="R166" s="174"/>
     </row>
     <row r="167" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="181"/>
-      <c r="B167" s="187"/>
+      <c r="B167" s="174"/>
       <c r="C167" s="45" t="s">
         <v>270</v>
       </c>
@@ -10128,8 +10128,8 @@
       <c r="E167" s="49">
         <v>0.25</v>
       </c>
-      <c r="F167" s="187"/>
-      <c r="G167" s="187"/>
+      <c r="F167" s="174"/>
+      <c r="G167" s="174"/>
       <c r="H167" s="22"/>
       <c r="I167" s="22"/>
       <c r="J167" s="22"/>
@@ -10138,20 +10138,20 @@
       <c r="M167" s="22"/>
       <c r="N167" s="22"/>
       <c r="O167" s="22"/>
-      <c r="P167" s="171"/>
+      <c r="P167" s="175"/>
       <c r="Q167" s="168"/>
-      <c r="R167" s="187"/>
+      <c r="R167" s="174"/>
     </row>
     <row r="168" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="181"/>
-      <c r="B168" s="187"/>
+      <c r="B168" s="174"/>
       <c r="C168" s="46" t="s">
         <v>271</v>
       </c>
       <c r="D168" s="60"/>
       <c r="E168" s="18"/>
-      <c r="F168" s="187"/>
-      <c r="G168" s="187"/>
+      <c r="F168" s="174"/>
+      <c r="G168" s="174"/>
       <c r="H168" s="22"/>
       <c r="I168" s="22"/>
       <c r="J168" s="22"/>
@@ -10160,20 +10160,20 @@
       <c r="M168" s="22"/>
       <c r="N168" s="22"/>
       <c r="O168" s="22"/>
-      <c r="P168" s="171"/>
-      <c r="Q168" s="171"/>
-      <c r="R168" s="187"/>
+      <c r="P168" s="175"/>
+      <c r="Q168" s="175"/>
+      <c r="R168" s="174"/>
     </row>
     <row r="169" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="181"/>
-      <c r="B169" s="187"/>
+      <c r="B169" s="174"/>
       <c r="C169" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D169" s="60"/>
       <c r="E169" s="18"/>
-      <c r="F169" s="187"/>
-      <c r="G169" s="187"/>
+      <c r="F169" s="174"/>
+      <c r="G169" s="174"/>
       <c r="H169" s="22"/>
       <c r="I169" s="22"/>
       <c r="J169" s="22"/>
@@ -10182,13 +10182,13 @@
       <c r="M169" s="22"/>
       <c r="N169" s="22"/>
       <c r="O169" s="22"/>
-      <c r="P169" s="171"/>
-      <c r="Q169" s="171"/>
-      <c r="R169" s="187"/>
+      <c r="P169" s="175"/>
+      <c r="Q169" s="175"/>
+      <c r="R169" s="174"/>
     </row>
     <row r="170" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="181"/>
-      <c r="B170" s="187"/>
+      <c r="B170" s="174"/>
       <c r="C170" s="47" t="s">
         <v>273</v>
       </c>
@@ -10197,8 +10197,8 @@
         <v>0</v>
       </c>
       <c r="E170" s="18"/>
-      <c r="F170" s="187"/>
-      <c r="G170" s="187"/>
+      <c r="F170" s="174"/>
+      <c r="G170" s="174"/>
       <c r="H170" s="22"/>
       <c r="I170" s="22"/>
       <c r="J170" s="22"/>
@@ -10207,13 +10207,13 @@
       <c r="M170" s="22"/>
       <c r="N170" s="22"/>
       <c r="O170" s="22"/>
-      <c r="P170" s="171"/>
+      <c r="P170" s="175"/>
       <c r="Q170" s="169"/>
-      <c r="R170" s="187"/>
+      <c r="R170" s="174"/>
     </row>
     <row r="171" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="181"/>
-      <c r="B171" s="187"/>
+      <c r="B171" s="174"/>
       <c r="C171" s="96" t="s">
         <v>274</v>
       </c>
@@ -10223,8 +10223,8 @@
       <c r="E171" s="114" t="s">
         <v>276</v>
       </c>
-      <c r="F171" s="187"/>
-      <c r="G171" s="187"/>
+      <c r="F171" s="174"/>
+      <c r="G171" s="174"/>
       <c r="H171" s="22"/>
       <c r="I171" s="22"/>
       <c r="J171" s="22"/>
@@ -10233,13 +10233,13 @@
       <c r="M171" s="22"/>
       <c r="N171" s="22"/>
       <c r="O171" s="22"/>
-      <c r="P171" s="171"/>
+      <c r="P171" s="175"/>
       <c r="Q171" s="153"/>
-      <c r="R171" s="187"/>
+      <c r="R171" s="174"/>
     </row>
     <row r="172" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="181"/>
-      <c r="B172" s="187"/>
+      <c r="B172" s="174"/>
       <c r="C172" s="66" t="s">
         <v>277</v>
       </c>
@@ -10249,8 +10249,8 @@
       <c r="E172" s="48">
         <v>1</v>
       </c>
-      <c r="F172" s="187"/>
-      <c r="G172" s="187"/>
+      <c r="F172" s="174"/>
+      <c r="G172" s="174"/>
       <c r="H172" s="22"/>
       <c r="I172" s="22"/>
       <c r="J172" s="22"/>
@@ -10259,13 +10259,13 @@
       <c r="M172" s="22"/>
       <c r="N172" s="22"/>
       <c r="O172" s="22"/>
-      <c r="P172" s="171"/>
+      <c r="P172" s="175"/>
       <c r="Q172" s="168"/>
-      <c r="R172" s="187"/>
+      <c r="R172" s="174"/>
     </row>
     <row r="173" spans="1:19" ht="350.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="71"/>
-      <c r="B173" s="187"/>
+      <c r="B173" s="174"/>
       <c r="C173" s="67"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
@@ -10279,9 +10279,9 @@
       <c r="M173" s="22"/>
       <c r="N173" s="22"/>
       <c r="O173" s="22"/>
-      <c r="P173" s="171"/>
+      <c r="P173" s="175"/>
       <c r="Q173" s="169"/>
-      <c r="R173" s="187"/>
+      <c r="R173" s="174"/>
     </row>
     <row r="174" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="70"/>
@@ -10301,12 +10301,12 @@
       <c r="O174" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="P174" s="171"/>
+      <c r="P174" s="175"/>
       <c r="Q174" s="157">
         <f>(Q140+Q143+Q146+Q148+Q150+Q152+Q154+Q156+Q158+Q160+Q162+Q167+Q172)/13</f>
         <v>0.45512307692307691</v>
       </c>
-      <c r="R174" s="187"/>
+      <c r="R174" s="174"/>
       <c r="S174" s="165" t="s">
         <v>279</v>
       </c>
@@ -10329,18 +10329,104 @@
       <c r="O175" s="162" t="s">
         <v>280</v>
       </c>
-      <c r="P175" s="171"/>
+      <c r="P175" s="175"/>
       <c r="Q175" s="158">
         <f>(Q43+Q50+Q72+Q85+Q98+Q111+Q138+Q174)/8</f>
         <v>0.6170062558275059</v>
       </c>
-      <c r="R175" s="187"/>
+      <c r="R175" s="174"/>
     </row>
     <row r="176" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A176" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="E87:E88"/>
+    <mergeCell ref="G87:G88"/>
+    <mergeCell ref="A2:A109"/>
+    <mergeCell ref="A139:A172"/>
+    <mergeCell ref="A112:A137"/>
+    <mergeCell ref="E3:E18"/>
+    <mergeCell ref="F140:F141"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="B2:B42"/>
+    <mergeCell ref="B51:B71"/>
+    <mergeCell ref="E143:E144"/>
+    <mergeCell ref="F143:F144"/>
+    <mergeCell ref="Q143:Q144"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="D87:D88"/>
+    <mergeCell ref="C5:C18"/>
+    <mergeCell ref="F122:F123"/>
+    <mergeCell ref="D103:D104"/>
+    <mergeCell ref="E113:E114"/>
+    <mergeCell ref="Q90:Q91"/>
+    <mergeCell ref="G113:G114"/>
+    <mergeCell ref="G143:G144"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="C22:C35"/>
+    <mergeCell ref="Q119:Q120"/>
+    <mergeCell ref="H48:H49"/>
+    <mergeCell ref="Q116:Q117"/>
+    <mergeCell ref="Q20:Q35"/>
+    <mergeCell ref="E52:E66"/>
+    <mergeCell ref="D140:D141"/>
+    <mergeCell ref="E122:E123"/>
+    <mergeCell ref="D52:D66"/>
+    <mergeCell ref="P2:P175"/>
+    <mergeCell ref="Q122:Q123"/>
+    <mergeCell ref="E103:E104"/>
+    <mergeCell ref="Q162:Q165"/>
+    <mergeCell ref="D20:D35"/>
+    <mergeCell ref="D116:D117"/>
+    <mergeCell ref="D143:D144"/>
+    <mergeCell ref="H119:H120"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="F109:F110"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="B86:B97"/>
+    <mergeCell ref="B112:B137"/>
+    <mergeCell ref="B139:B173"/>
+    <mergeCell ref="B73:B84"/>
+    <mergeCell ref="Q172:Q173"/>
+    <mergeCell ref="E106:E107"/>
+    <mergeCell ref="F161:G172"/>
+    <mergeCell ref="G140:G141"/>
+    <mergeCell ref="Q41:Q42"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="B99:B110"/>
+    <mergeCell ref="G116:G117"/>
+    <mergeCell ref="Q52:Q66"/>
+    <mergeCell ref="C53:C66"/>
+    <mergeCell ref="F113:F114"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="Q109:Q110"/>
+    <mergeCell ref="E70:E71"/>
+    <mergeCell ref="Q70:Q71"/>
+    <mergeCell ref="Q48:Q49"/>
+    <mergeCell ref="F3:F18"/>
+    <mergeCell ref="Q140:Q141"/>
+    <mergeCell ref="F87:F88"/>
+    <mergeCell ref="D119:D120"/>
+    <mergeCell ref="Q106:Q107"/>
+    <mergeCell ref="F119:F120"/>
+    <mergeCell ref="Q87:Q88"/>
+    <mergeCell ref="D109:D110"/>
+    <mergeCell ref="G52:G66"/>
+    <mergeCell ref="F103:F104"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="D113:D114"/>
+    <mergeCell ref="F116:F117"/>
+    <mergeCell ref="F20:F35"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="G48:G49"/>
+    <mergeCell ref="D3:D18"/>
+    <mergeCell ref="E140:E141"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="Q103:Q104"/>
     <mergeCell ref="Q113:Q114"/>
@@ -10365,92 +10451,6 @@
     <mergeCell ref="E100:E101"/>
     <mergeCell ref="E109:E110"/>
     <mergeCell ref="Q100:Q101"/>
-    <mergeCell ref="Q109:Q110"/>
-    <mergeCell ref="E70:E71"/>
-    <mergeCell ref="Q70:Q71"/>
-    <mergeCell ref="Q48:Q49"/>
-    <mergeCell ref="F3:F18"/>
-    <mergeCell ref="Q140:Q141"/>
-    <mergeCell ref="F87:F88"/>
-    <mergeCell ref="D119:D120"/>
-    <mergeCell ref="Q106:Q107"/>
-    <mergeCell ref="F119:F120"/>
-    <mergeCell ref="Q87:Q88"/>
-    <mergeCell ref="D109:D110"/>
-    <mergeCell ref="G52:G66"/>
-    <mergeCell ref="F103:F104"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="F70:F71"/>
-    <mergeCell ref="D113:D114"/>
-    <mergeCell ref="F116:F117"/>
-    <mergeCell ref="F20:F35"/>
-    <mergeCell ref="D100:D101"/>
-    <mergeCell ref="Q162:Q165"/>
-    <mergeCell ref="D20:D35"/>
-    <mergeCell ref="D116:D117"/>
-    <mergeCell ref="D143:D144"/>
-    <mergeCell ref="H119:H120"/>
-    <mergeCell ref="F100:F101"/>
-    <mergeCell ref="F109:F110"/>
-    <mergeCell ref="B44:B49"/>
-    <mergeCell ref="B86:B97"/>
-    <mergeCell ref="B112:B137"/>
-    <mergeCell ref="B139:B173"/>
-    <mergeCell ref="B73:B84"/>
-    <mergeCell ref="Q172:Q173"/>
-    <mergeCell ref="E106:E107"/>
-    <mergeCell ref="F161:G172"/>
-    <mergeCell ref="G140:G141"/>
-    <mergeCell ref="Q41:Q42"/>
-    <mergeCell ref="D90:D91"/>
-    <mergeCell ref="B99:B110"/>
-    <mergeCell ref="G116:G117"/>
-    <mergeCell ref="Q52:Q66"/>
-    <mergeCell ref="C53:C66"/>
-    <mergeCell ref="F113:F114"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="Q143:Q144"/>
-    <mergeCell ref="H45:H46"/>
-    <mergeCell ref="D87:D88"/>
-    <mergeCell ref="C5:C18"/>
-    <mergeCell ref="F122:F123"/>
-    <mergeCell ref="D103:D104"/>
-    <mergeCell ref="E113:E114"/>
-    <mergeCell ref="Q90:Q91"/>
-    <mergeCell ref="G113:G114"/>
-    <mergeCell ref="G143:G144"/>
-    <mergeCell ref="E41:E42"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="C22:C35"/>
-    <mergeCell ref="Q119:Q120"/>
-    <mergeCell ref="H48:H49"/>
-    <mergeCell ref="Q116:Q117"/>
-    <mergeCell ref="Q20:Q35"/>
-    <mergeCell ref="E52:E66"/>
-    <mergeCell ref="D140:D141"/>
-    <mergeCell ref="E122:E123"/>
-    <mergeCell ref="D52:D66"/>
-    <mergeCell ref="P2:P175"/>
-    <mergeCell ref="Q122:Q123"/>
-    <mergeCell ref="E103:E104"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="G48:G49"/>
-    <mergeCell ref="D3:D18"/>
-    <mergeCell ref="E140:E141"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="E87:E88"/>
-    <mergeCell ref="G87:G88"/>
-    <mergeCell ref="A2:A109"/>
-    <mergeCell ref="A139:A172"/>
-    <mergeCell ref="A112:A137"/>
-    <mergeCell ref="E3:E18"/>
-    <mergeCell ref="F140:F141"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="B2:B42"/>
-    <mergeCell ref="B51:B71"/>
-    <mergeCell ref="E143:E144"/>
-    <mergeCell ref="F143:F144"/>
   </mergeCells>
   <dataValidations count="22">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3 Q20" xr:uid="{00000000-0002-0000-0000-000000000000}">
